--- a/conferences_2026-07-05.xlsx
+++ b/conferences_2026-07-05.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S130"/>
+  <dimension ref="A1:S142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -6881,17 +6881,17 @@
     <row r="68">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>grc-plasmonics-nano-2026</t>
+          <t>meta-2026-dublin</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Gordon Research Conference — Plasmonics and Nanophotonics 2026</t>
+          <t>META 2026 — 16th International Conference on Metamaterials, Photonic Crystals and Plasmonics</t>
         </is>
       </c>
       <c r="C68" s="7" t="inlineStr">
         <is>
-          <t>GRC PNP 2026</t>
+          <t>META 2026</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -6901,27 +6901,27 @@
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>nanophotonics;plasmonics;quantum optics;2D-material photonics</t>
+          <t>nanophotonics;plasmonics</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>Newry, ME, USA</t>
+          <t>Dublin, Ireland</t>
         </is>
       </c>
       <c r="I68" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="J68" s="7" t="inlineStr">
@@ -6931,25 +6931,25 @@
       </c>
       <c r="K68" s="7" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="L68" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="M68" s="7" t="inlineStr">
         <is>
-          <t>https://www.grc.org/plasmonics-and-nanophotonics-conference/2026/</t>
-        </is>
-      </c>
-      <c r="N68" s="4" t="n">
-        <v>5</v>
+          <t>https://metaconferences.org/META26/</t>
+        </is>
+      </c>
+      <c r="N68" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="O68" s="7" t="inlineStr">
         <is>
-          <t>GRC on quantum nanophotonics, plasmonics and 2D photonics — highly relevant to AG Schuck</t>
+          <t>Major long-running metamaterials/plasmonics/nanophotonics conference with dedicated quantum-photonics sessions</t>
         </is>
       </c>
       <c r="P68" s="7" t="inlineStr">
@@ -6964,44 +6964,44 @@
       </c>
       <c r="R68" s="7" t="inlineStr">
         <is>
-          <t>application deadline 2026-06-21 has passed; late applicants only via chair approval/waitlist</t>
+          <t>new entry</t>
         </is>
       </c>
       <c r="S68" s="7" t="inlineStr">
         <is>
-          <t>https://www.grc.org/plasmonics-and-nanophotonics-conference/2026/</t>
+          <t>https://metaconferences.org/META26/index.php/META/dates</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>cewqo-2026</t>
+          <t>grc-plasmonics-nano-2026</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>30th Central European Workshop on Quantum Optics</t>
+          <t>Gordon Research Conference — Plasmonics and Nanophotonics 2026</t>
         </is>
       </c>
       <c r="C69" s="7" t="inlineStr">
         <is>
-          <t>CEWQO30 2026</t>
+          <t>GRC PNP 2026</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>quantum optics;single-photon sources;nonlinear optics;integrated quantum photonics</t>
+          <t>nanophotonics;plasmonics;quantum optics;2D-material photonics</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>Erlangen, Germany</t>
+          <t>Newry, ME, USA</t>
         </is>
       </c>
       <c r="I69" s="7" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="K69" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="L69" s="7" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="M69" s="7" t="inlineStr">
         <is>
-          <t>https://www.lightmatter.fau.de/2026/04/cewqo30-the-30th-central-european-workshop-on-quantum-optics-2026/</t>
+          <t>https://www.grc.org/plasmonics-and-nanophotonics-conference/2026/</t>
         </is>
       </c>
       <c r="N69" s="4" t="n">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="O69" s="7" t="inlineStr">
         <is>
-          <t>European quantum optics workshop co-hosted by FAU/MPL Erlangen — close to Münster</t>
+          <t>GRC on quantum nanophotonics, plasmonics and 2D photonics — highly relevant to AG Schuck</t>
         </is>
       </c>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>cfp_closed</t>
         </is>
       </c>
       <c r="Q69" s="7" t="inlineStr">
@@ -7059,54 +7059,54 @@
       </c>
       <c r="R69" s="7" t="inlineStr">
         <is>
-          <t>new entry; Jul 20-24 Erlangen, hosted by Chekhova/Marquardt groups</t>
+          <t>application deadline 2026-06-21 has passed; late applicants only via chair approval/waitlist</t>
         </is>
       </c>
       <c r="S69" s="7" t="inlineStr">
         <is>
-          <t>https://www.lightmatter.fau.de/2026/04/cewqo30-the-30th-central-european-workshop-on-quantum-optics-2026/; https://www.oqt.nat.fau.de/events/</t>
+          <t>https://www.grc.org/plasmonics-and-nanophotonics-conference/2026/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>apc-2026</t>
+          <t>cewqo-2026</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Optica Advanced Photonics Congress 2026</t>
+          <t>30th Central European Workshop on Quantum Optics</t>
         </is>
       </c>
       <c r="C70" s="7" t="inlineStr">
         <is>
-          <t>APC 2026</t>
+          <t>CEWQO30 2026</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>integrated quantum photonics;nonlinear optics;nanophotonics</t>
+          <t>quantum optics;single-photon sources;nonlinear optics;integrated quantum photonics</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>Long Beach, CA, USA</t>
+          <t>Erlangen, Germany</t>
         </is>
       </c>
       <c r="I70" s="7" t="inlineStr">
@@ -7114,9 +7114,9 @@
           <t>TBA</t>
         </is>
       </c>
-      <c r="J70" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
+      <c r="J70" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K70" s="7" t="inlineStr">
@@ -7126,25 +7126,25 @@
       </c>
       <c r="L70" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="M70" s="7" t="inlineStr">
         <is>
-          <t>https://www.optica.org/events/congress/advanced_photonics_congress/</t>
-        </is>
-      </c>
-      <c r="N70" s="6" t="n">
-        <v>4</v>
+          <t>https://www.lightmatter.fau.de/2026/04/cewqo30-the-30th-central-european-workshop-on-quantum-optics-2026/</t>
+        </is>
+      </c>
+      <c r="N70" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="O70" s="7" t="inlineStr">
         <is>
-          <t>Optica congress including nonlinear photonics, waveguides and integrated circuits</t>
+          <t>European quantum optics workshop co-hosted by FAU/MPL Erlangen — close to Münster</t>
         </is>
       </c>
       <c r="P70" s="7" t="inlineStr">
         <is>
-          <t>cfp_open</t>
+          <t>upcoming</t>
         </is>
       </c>
       <c r="Q70" s="7" t="inlineStr">
@@ -7154,29 +7154,29 @@
       </c>
       <c r="R70" s="7" t="inlineStr">
         <is>
-          <t>venue confirmed: Long Beach, CA (Hilton Long Beach); regular CFP closed, postdeadline paper window open through 2026-07-07</t>
+          <t>new entry; Jul 20-24 Erlangen, hosted by Chekhova/Marquardt groups</t>
         </is>
       </c>
       <c r="S70" s="7" t="inlineStr">
         <is>
-          <t>https://www.optica.org/events/congress/advanced_photonics_congress/</t>
+          <t>https://www.lightmatter.fau.de/2026/04/cewqo30-the-30th-central-european-workshop-on-quantum-optics-2026/; https://www.oqt.nat.fau.de/events/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>ipr-2026</t>
+          <t>apc-2026</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Integrated Photonics Research, Silicon and Nanophotonics 2026</t>
+          <t>Optica Advanced Photonics Congress 2026</t>
         </is>
       </c>
       <c r="C71" s="7" t="inlineStr">
         <is>
-          <t>IPR 2026</t>
+          <t>APC 2026</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>integrated quantum photonics;photonic integrated circuits;silicon photonics;nanophotonics</t>
+          <t>integrated quantum photonics;nonlinear optics;nanophotonics</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -7226,15 +7226,15 @@
       </c>
       <c r="M71" s="7" t="inlineStr">
         <is>
-          <t>https://www.optica.org/events/congress/advanced_photonics_congress/program/integrated_photonics_research_silicon_and_nanophot/</t>
-        </is>
-      </c>
-      <c r="N71" s="4" t="n">
-        <v>5</v>
+          <t>https://www.optica.org/events/congress/advanced_photonics_congress/</t>
+        </is>
+      </c>
+      <c r="N71" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="O71" s="7" t="inlineStr">
         <is>
-          <t>Optica's dedicated integrated/nanophotonics topical meeting, with an explicit integrated nonlinear-and-quantum-optics track; co-located with APC 2026</t>
+          <t>Optica congress including nonlinear photonics, waveguides and integrated circuits</t>
         </is>
       </c>
       <c r="P71" s="7" t="inlineStr">
@@ -7249,64 +7249,64 @@
       </c>
       <c r="R71" s="7" t="inlineStr">
         <is>
-          <t>new entry; co-located with apc-2026, distinct topical track</t>
+          <t>venue confirmed: Long Beach, CA (Hilton Long Beach); regular CFP closed, postdeadline paper window open through 2026-07-07</t>
         </is>
       </c>
       <c r="S71" s="7" t="inlineStr">
         <is>
-          <t>https://www.optica.org/events/congress/advanced_photonics_congress/program/integrated_photonics_research_silicon_and_nanophot/</t>
+          <t>https://www.optica.org/events/congress/advanced_photonics_congress/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>lake-como-ufqp-2026</t>
+          <t>ipr-2026</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>New Frontiers in Ultrafast Quantum Optics — Lake Como School</t>
+          <t>Integrated Photonics Research, Silicon and Nanophotonics 2026</t>
         </is>
       </c>
       <c r="C72" s="7" t="inlineStr">
         <is>
-          <t>UFQP 2026</t>
+          <t>IPR 2026</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>Summer School</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>quantum optics;nonlinear optics;single-photon sources</t>
+          <t>integrated quantum photonics;photonic integrated circuits;silicon photonics;nanophotonics</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>Como, Italy</t>
+          <t>Long Beach, CA, USA</t>
         </is>
       </c>
       <c r="I72" s="7" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="J72" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="J72" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="K72" s="7" t="inlineStr">
@@ -7316,25 +7316,25 @@
       </c>
       <c r="L72" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="M72" s="7" t="inlineStr">
         <is>
-          <t>https://ufqp.lakecomoschool.org/</t>
-        </is>
-      </c>
-      <c r="N72" s="6" t="n">
-        <v>4</v>
+          <t>https://www.optica.org/events/congress/advanced_photonics_congress/program/integrated_photonics_research_silicon_and_nanophot/</t>
+        </is>
+      </c>
+      <c r="N72" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="O72" s="7" t="inlineStr">
         <is>
-          <t>Summer school on ultrafast quantum optics — photon correlations and time-frequency entanglement</t>
+          <t>Optica's dedicated integrated/nanophotonics topical meeting, with an explicit integrated nonlinear-and-quantum-optics track; co-located with APC 2026</t>
         </is>
       </c>
       <c r="P72" s="7" t="inlineStr">
         <is>
-          <t>cfp_closed</t>
+          <t>cfp_open</t>
         </is>
       </c>
       <c r="Q72" s="7" t="inlineStr">
@@ -7344,29 +7344,29 @@
       </c>
       <c r="R72" s="7" t="inlineStr">
         <is>
-          <t>application deadline 2026-05-31 confirmed passed; school (max 40 participants) still listed as scheduled, no cancellation signal</t>
+          <t>new entry; co-located with apc-2026, distinct topical track</t>
         </is>
       </c>
       <c r="S72" s="7" t="inlineStr">
         <is>
-          <t>https://ufqp.lakecomoschool.org/; https://www.quantiki.org/conference/summer-school-new-frontiers-ultrafast-quantum-optics</t>
+          <t>https://www.optica.org/events/congress/advanced_photonics_congress/program/integrated_photonics_research_silicon_and_nanophot/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>benasque-ftqt-2026</t>
+          <t>mpi-frontiers-light-matter-2026</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Fault-Tolerant Quantum Technologies 2026</t>
+          <t>Workshop on the Frontiers in Light-Matter Interactions 2026</t>
         </is>
       </c>
       <c r="C73" s="7" t="inlineStr">
         <is>
-          <t>Benasque FTQT</t>
+          <t>MPI FLMI</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -7376,27 +7376,27 @@
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>quantum computing hardware;quantum optics</t>
+          <t>nanophotonics;plasmonics</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>Benasque, Spain</t>
+          <t>Germany (Max Planck Institute)</t>
         </is>
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J73" s="7" t="inlineStr">
@@ -7411,20 +7411,20 @@
       </c>
       <c r="L73" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="M73" s="7" t="inlineStr">
         <is>
-          <t>https://www.benasque.org/2026ftqt/</t>
-        </is>
-      </c>
-      <c r="N73" s="3" t="n">
-        <v>2</v>
+          <t>https://plan.events.mpg.de/event/676/</t>
+        </is>
+      </c>
+      <c r="N73" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="O73" s="7" t="inlineStr">
         <is>
-          <t>Biennial QEC/fault-tolerance workshop sponsored by photonic-quantum-computing firms (PsiQuantum, Xanadu)</t>
+          <t>MPI-hosted workshop on nanophotonics/metasurfaces/near-field nano-optics, directly overlapping the group's nanophotonics interests</t>
         </is>
       </c>
       <c r="P73" s="7" t="inlineStr">
@@ -7444,24 +7444,24 @@
       </c>
       <c r="S73" s="7" t="inlineStr">
         <is>
-          <t>https://www.benasque.org/2026ftqt/</t>
+          <t>https://plan.events.mpg.de/event/676/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>cargese-topfrac-2026</t>
+          <t>lake-como-ufqp-2026</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Topology and Fractionalisation in Quantum Matter and Synthetic Platforms</t>
+          <t>New Frontiers in Ultrafast Quantum Optics — Lake Como School</t>
         </is>
       </c>
       <c r="C74" s="7" t="inlineStr">
         <is>
-          <t>TopFrac 2026</t>
+          <t>UFQP 2026</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
@@ -7471,27 +7471,27 @@
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>nanophotonics;quantum optics</t>
+          <t>quantum optics;nonlinear optics;single-photon sources</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>Cargèse, France</t>
+          <t>Como, Italy</t>
         </is>
       </c>
       <c r="I74" s="7" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="J74" s="7" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="K74" s="7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="L74" s="7" t="inlineStr">
@@ -7511,20 +7511,20 @@
       </c>
       <c r="M74" s="7" t="inlineStr">
         <is>
-          <t>https://topfrac-cargese.sciencesconf.org/</t>
-        </is>
-      </c>
-      <c r="N74" s="5" t="n">
-        <v>3</v>
+          <t>https://ufqp.lakecomoschool.org/</t>
+        </is>
+      </c>
+      <c r="N74" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="O74" s="7" t="inlineStr">
         <is>
-          <t>CECAM/IESC school on topological and synthetic quantum platforms, incl. photonic/synthetic-dimension simulators</t>
+          <t>Summer school on ultrafast quantum optics — photon correlations and time-frequency entanglement</t>
         </is>
       </c>
       <c r="P74" s="7" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>cfp_closed</t>
         </is>
       </c>
       <c r="Q74" s="7" t="inlineStr">
@@ -7534,54 +7534,54 @@
       </c>
       <c r="R74" s="7" t="inlineStr">
         <is>
-          <t>new entry</t>
+          <t>application deadline 2026-05-31 confirmed passed; school (max 40 participants) still listed as scheduled, no cancellation signal</t>
         </is>
       </c>
       <c r="S74" s="7" t="inlineStr">
         <is>
-          <t>https://topfrac-cargese.sciencesconf.org/</t>
+          <t>https://ufqp.lakecomoschool.org/; https://www.quantiki.org/conference/summer-school-new-frontiers-ultrafast-quantum-optics</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>ieee-rapid-2026</t>
+          <t>benasque-ftqt-2026</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>IEEE Research and Applications of Photonics in Defense 2026</t>
+          <t>Fault-Tolerant Quantum Technologies 2026</t>
         </is>
       </c>
       <c r="C75" s="7" t="inlineStr">
         <is>
-          <t>IEEE RAPID 2026</t>
+          <t>Benasque FTQT</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>single-photon sources;quantum communication</t>
+          <t>quantum computing hardware;quantum optics</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>Miramar Beach, FL, USA</t>
+          <t>Benasque, Spain</t>
         </is>
       </c>
       <c r="I75" s="7" t="inlineStr">
@@ -7591,7 +7591,7 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K75" s="7" t="inlineStr">
@@ -7601,12 +7601,12 @@
       </c>
       <c r="L75" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="M75" s="7" t="inlineStr">
         <is>
-          <t>https://ieee-rapid.org/</t>
+          <t>https://www.benasque.org/2026ftqt/</t>
         </is>
       </c>
       <c r="N75" s="3" t="n">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="O75" s="7" t="inlineStr">
         <is>
-          <t>Defense photonics; some single-photon sensing sessions</t>
+          <t>Biennial QEC/fault-tolerance workshop sponsored by photonic-quantum-computing firms (PsiQuantum, Xanadu)</t>
         </is>
       </c>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>cfp_closed</t>
+          <t>upcoming</t>
         </is>
       </c>
       <c r="Q75" s="7" t="inlineStr">
@@ -7629,59 +7629,59 @@
       </c>
       <c r="R75" s="7" t="inlineStr">
         <is>
-          <t>paper submission deadline confirmed 2026-02-16 (passed)</t>
+          <t>new entry</t>
         </is>
       </c>
       <c r="S75" s="7" t="inlineStr">
         <is>
-          <t>https://ieee-rapid.org/</t>
+          <t>https://www.benasque.org/2026ftqt/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>benasque-qels-2026</t>
+          <t>cargese-topfrac-2026</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>Quantum Engineering of Levitated Systems 2026</t>
+          <t>Topology and Fractionalisation in Quantum Matter and Synthetic Platforms</t>
         </is>
       </c>
       <c r="C76" s="7" t="inlineStr">
         <is>
-          <t>Benasque QELS</t>
+          <t>TopFrac 2026</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Summer School</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>optomechanics;nanophotonics;quantum optics</t>
+          <t>nanophotonics;quantum optics</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>Benasque, Spain</t>
+          <t>Cargèse, France</t>
         </is>
       </c>
       <c r="I76" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="J76" s="7" t="inlineStr">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="K76" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="L76" s="7" t="inlineStr">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="M76" s="7" t="inlineStr">
         <is>
-          <t>https://www.benasque.org/2026qels/</t>
+          <t>https://topfrac-cargese.sciencesconf.org/</t>
         </is>
       </c>
       <c r="N76" s="5" t="n">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="O76" s="7" t="inlineStr">
         <is>
-          <t>10th-anniversary workshop at the interface of quantum optics and nanophotonics (levitated optomechanics)</t>
+          <t>CECAM/IESC school on topological and synthetic quantum platforms, incl. photonic/synthetic-dimension simulators</t>
         </is>
       </c>
       <c r="P76" s="7" t="inlineStr">
@@ -7729,49 +7729,49 @@
       </c>
       <c r="S76" s="7" t="inlineStr">
         <is>
-          <t>https://www.benasque.org/2026qels/; https://www.quantiki.org/conference/quantum-engineering-levitated-systems</t>
+          <t>https://topfrac-cargese.sciencesconf.org/</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>cargese-metaquantm-2026</t>
+          <t>ieee-rapid-2026</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>MetaQuantM 2026: Creation and Manipulation of New States of Metastable Quantum Matter</t>
+          <t>IEEE Research and Applications of Photonics in Defense 2026</t>
         </is>
       </c>
       <c r="C77" s="7" t="inlineStr">
         <is>
-          <t>MetaQuantM 2026</t>
+          <t>IEEE RAPID 2026</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>Summer School</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>quantum optics;nanophotonics</t>
+          <t>single-photon sources;quantum communication</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>Cargèse, France</t>
+          <t>Miramar Beach, FL, USA</t>
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="K77" s="7" t="inlineStr">
@@ -7791,25 +7791,25 @@
       </c>
       <c r="L77" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="M77" s="7" t="inlineStr">
         <is>
-          <t>https://metaquantm.ijs.si/</t>
-        </is>
-      </c>
-      <c r="N77" s="5" t="n">
-        <v>3</v>
+          <t>https://ieee-rapid.org/</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="O77" s="7" t="inlineStr">
         <is>
-          <t>Covers polariton condensates, strong light-matter coupling and non-Hermitian quantum-optical dynamics</t>
+          <t>Defense photonics; some single-photon sensing sessions</t>
         </is>
       </c>
       <c r="P77" s="7" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>cfp_closed</t>
         </is>
       </c>
       <c r="Q77" s="7" t="inlineStr">
@@ -7819,54 +7819,54 @@
       </c>
       <c r="R77" s="7" t="inlineStr">
         <is>
-          <t>new entry</t>
+          <t>paper submission deadline confirmed 2026-02-16 (passed)</t>
         </is>
       </c>
       <c r="S77" s="7" t="inlineStr">
         <is>
-          <t>https://metaquantm.ijs.si/</t>
+          <t>https://ieee-rapid.org/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>spie-op-2026</t>
+          <t>benasque-qels-2026</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>SPIE Optics + Photonics 2026</t>
+          <t>Quantum Engineering of Levitated Systems 2026</t>
         </is>
       </c>
       <c r="C78" s="7" t="inlineStr">
         <is>
-          <t>SPIE O+P 2026</t>
+          <t>Benasque QELS</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>integrated quantum photonics;nanophotonics;quantum optics;single-photon sources</t>
+          <t>optomechanics;nanophotonics;quantum optics</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>San Diego, CA, USA</t>
+          <t>Benasque, Spain</t>
         </is>
       </c>
       <c r="I78" s="7" t="inlineStr">
@@ -7876,7 +7876,7 @@
       </c>
       <c r="J78" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K78" s="7" t="inlineStr">
@@ -7886,20 +7886,20 @@
       </c>
       <c r="L78" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="M78" s="7" t="inlineStr">
         <is>
-          <t>https://spie.org/optics-and-photonics</t>
-        </is>
-      </c>
-      <c r="N78" s="6" t="n">
-        <v>4</v>
+          <t>https://www.benasque.org/2026qels/</t>
+        </is>
+      </c>
+      <c r="N78" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="O78" s="7" t="inlineStr">
         <is>
-          <t>SPIE major annual meeting with quantum nanophotonics and quantum technologies tracks</t>
+          <t>10th-anniversary workshop at the interface of quantum optics and nanophotonics (levitated optomechanics)</t>
         </is>
       </c>
       <c r="P78" s="7" t="inlineStr">
@@ -7914,64 +7914,64 @@
       </c>
       <c r="R78" s="7" t="inlineStr">
         <is>
-          <t>no change</t>
+          <t>new entry</t>
         </is>
       </c>
       <c r="S78" s="7" t="inlineStr">
         <is>
-          <t>https://spie.org/optics-and-photonics</t>
+          <t>https://www.benasque.org/2026qels/; https://www.quantiki.org/conference/quantum-engineering-levitated-systems</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>eosam-2026</t>
+          <t>cargese-metaquantm-2026</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>European Optical Society Annual Meeting 2026</t>
+          <t>MetaQuantM 2026: Creation and Manipulation of New States of Metastable Quantum Matter</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
         <is>
-          <t>EOSAM 2026</t>
+          <t>MetaQuantM 2026</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Summer School</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>integrated quantum photonics;nanophotonics;nonlinear optics</t>
+          <t>quantum optics;nanophotonics</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>Tampere, Finland</t>
+          <t>Cargèse, France</t>
         </is>
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K79" s="7" t="inlineStr">
@@ -7981,25 +7981,25 @@
       </c>
       <c r="L79" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="M79" s="7" t="inlineStr">
         <is>
-          <t>https://www.europeanoptics.org/events/eos/eosam2026.html</t>
-        </is>
-      </c>
-      <c r="N79" s="6" t="n">
-        <v>4</v>
+          <t>https://metaquantm.ijs.si/</t>
+        </is>
+      </c>
+      <c r="N79" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="O79" s="7" t="inlineStr">
         <is>
-          <t>EOS flagship European photonics meeting with strong quantum photonics programme</t>
+          <t>Covers polariton condensates, strong light-matter coupling and non-Hermitian quantum-optical dynamics</t>
         </is>
       </c>
       <c r="P79" s="7" t="inlineStr">
         <is>
-          <t>cfp_closed</t>
+          <t>upcoming</t>
         </is>
       </c>
       <c r="Q79" s="7" t="inlineStr">
@@ -8009,29 +8009,29 @@
       </c>
       <c r="R79" s="7" t="inlineStr">
         <is>
-          <t>main abstract deadline 2026-04-14 and early-bird 2026-06-15 both passed; late/post-deadline poster window remains open through 2026-07-15</t>
+          <t>new entry</t>
         </is>
       </c>
       <c r="S79" s="7" t="inlineStr">
         <is>
-          <t>https://www.europeanoptics.org/events/eos/eosam2026.html</t>
+          <t>https://metaquantm.ijs.si/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>qcrypt-2026</t>
+          <t>spie-op-2026</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>QCrypt 2026</t>
+          <t>SPIE Optics + Photonics 2026</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>QCrypt 2026</t>
+          <t>SPIE O+P 2026</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
@@ -8041,22 +8041,22 @@
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>quantum communication;QKD;quantum networking</t>
+          <t>integrated quantum photonics;nanophotonics;quantum optics;single-photon sources</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>Ottawa, Canada</t>
+          <t>San Diego, CA, USA</t>
         </is>
       </c>
       <c r="I80" s="7" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="J80" s="7" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="K80" s="7" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="M80" s="7" t="inlineStr">
         <is>
-          <t>https://qcrypt.net/2026/</t>
+          <t>https://spie.org/optics-and-photonics</t>
         </is>
       </c>
       <c r="N80" s="6" t="n">
@@ -8089,12 +8089,12 @@
       </c>
       <c r="O80" s="7" t="inlineStr">
         <is>
-          <t>Premier annual QKD and quantum cryptography conference</t>
+          <t>SPIE major annual meeting with quantum nanophotonics and quantum technologies tracks</t>
         </is>
       </c>
       <c r="P80" s="7" t="inlineStr">
         <is>
-          <t>cfp_closed</t>
+          <t>upcoming</t>
         </is>
       </c>
       <c r="Q80" s="7" t="inlineStr">
@@ -8104,64 +8104,64 @@
       </c>
       <c r="R80" s="7" t="inlineStr">
         <is>
-          <t>talk submission deadline 2026-03-13 and poster deadline 2026-05-01 both confirmed passed; venue: Learning Crossroads (CRX), University of Ottawa</t>
+          <t>no change</t>
         </is>
       </c>
       <c r="S80" s="7" t="inlineStr">
         <is>
-          <t>https://qcrypt.net/2026/</t>
+          <t>https://spie.org/optics-and-photonics</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>isopc-erice-2026</t>
+          <t>eosam-2026</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>International School on Physical Computing — Metaphotonics and Optical Neural Networks</t>
+          <t>European Optical Society Annual Meeting 2026</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>ISOPC 2026</t>
+          <t>EOSAM 2026</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>Summer School</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>integrated quantum photonics;nanophotonics;photonic integrated circuits</t>
+          <t>integrated quantum photonics;nanophotonics;nonlinear optics</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>Erice, Italy</t>
+          <t>Tampere, Finland</t>
         </is>
       </c>
       <c r="I81" s="7" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="K81" s="7" t="inlineStr">
@@ -8171,25 +8171,25 @@
       </c>
       <c r="L81" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="M81" s="7" t="inlineStr">
         <is>
-          <t>https://www.lso.uni-hannover.de/en/isopc</t>
-        </is>
-      </c>
-      <c r="N81" s="4" t="n">
-        <v>5</v>
+          <t>https://www.europeanoptics.org/events/eos/eosam2026.html</t>
+        </is>
+      </c>
+      <c r="N81" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="O81" s="7" t="inlineStr">
         <is>
-          <t>Ettore Majorana Foundation school directed by Calà Lesina &amp; Pernice, directly on metaphotonics, integrated photonic platforms and optical neural networks</t>
+          <t>EOS flagship European photonics meeting with strong quantum photonics programme</t>
         </is>
       </c>
       <c r="P81" s="7" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>cfp_closed</t>
         </is>
       </c>
       <c r="Q81" s="7" t="inlineStr">
@@ -8199,29 +8199,29 @@
       </c>
       <c r="R81" s="7" t="inlineStr">
         <is>
-          <t>new entry</t>
+          <t>main abstract deadline 2026-04-14 and early-bird 2026-06-15 both passed; late/post-deadline poster window remains open through 2026-07-15</t>
         </is>
       </c>
       <c r="S81" s="7" t="inlineStr">
         <is>
-          <t>https://www.lso.uni-hannover.de/en/isopc; https://konferenz.uni-hannover.de/event/222/</t>
+          <t>https://www.europeanoptics.org/events/eos/eosam2026.html</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>tqc-2026</t>
+          <t>qcrypt-2026</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Theory of Quantum Computation, Communication and Cryptography 2026</t>
+          <t>QCrypt 2026</t>
         </is>
       </c>
       <c r="C82" s="7" t="inlineStr">
         <is>
-          <t>TQC 2026</t>
+          <t>QCrypt 2026</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
@@ -8231,32 +8231,32 @@
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>quantum communication;quantum computing hardware;quantum networking</t>
+          <t>quantum communication;QKD;quantum networking</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>Sherbrooke, QC, Canada</t>
+          <t>Ottawa, Canada</t>
         </is>
       </c>
       <c r="I82" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="J82" s="7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="K82" s="7" t="inlineStr">
@@ -8266,20 +8266,20 @@
       </c>
       <c r="L82" s="7" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="M82" s="7" t="inlineStr">
         <is>
-          <t>https://tqc-conference.org/2026/</t>
-        </is>
-      </c>
-      <c r="N82" s="5" t="n">
-        <v>3</v>
+          <t>https://qcrypt.net/2026/</t>
+        </is>
+      </c>
+      <c r="N82" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="O82" s="7" t="inlineStr">
         <is>
-          <t>Theory conference for quantum communication, computation and cryptography</t>
+          <t>Premier annual QKD and quantum cryptography conference</t>
         </is>
       </c>
       <c r="P82" s="7" t="inlineStr">
@@ -8294,92 +8294,92 @@
       </c>
       <c r="R82" s="7" t="inlineStr">
         <is>
-          <t>main submission deadline 2026-02-01 (AoE) and early-bird registration 2026-06-28 both confirmed passed; poster-only track closed 2026-04-20</t>
+          <t>talk submission deadline 2026-03-13 and poster deadline 2026-05-01 both confirmed passed; venue: Learning Crossroads (CRX), University of Ottawa</t>
         </is>
       </c>
       <c r="S82" s="7" t="inlineStr">
         <is>
-          <t>https://tqc-conference.org/2026/</t>
+          <t>https://qcrypt.net/2026/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>asc-2026</t>
+          <t>isopc-erice-2026</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Applied Superconductivity Conference 2026</t>
+          <t>International School on Physical Computing — Metaphotonics and Optical Neural Networks</t>
         </is>
       </c>
       <c r="C83" s="7" t="inlineStr">
         <is>
-          <t>ASC 2026</t>
+          <t>ISOPC 2026</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Summer School</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>SNSPDs;cryogenic electronics;single-photon sources</t>
+          <t>integrated quantum photonics;nanophotonics;photonic integrated circuits</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, USA</t>
+          <t>Erice, Italy</t>
         </is>
       </c>
       <c r="I83" s="7" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="K83" s="9" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="L83" s="9" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K83" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="L83" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
         </is>
       </c>
       <c r="M83" s="7" t="inlineStr">
         <is>
-          <t>https://appliedsuperconductivity.org/asc2026/</t>
-        </is>
-      </c>
-      <c r="N83" s="6" t="n">
-        <v>4</v>
+          <t>https://www.lso.uni-hannover.de/en/isopc</t>
+        </is>
+      </c>
+      <c r="N83" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="O83" s="7" t="inlineStr">
         <is>
-          <t>Premier superconductivity conference with major SNSPD and cryogenic electronics sessions</t>
+          <t>Ettore Majorana Foundation school directed by Calà Lesina &amp; Pernice, directly on metaphotonics, integrated photonic platforms and optical neural networks</t>
         </is>
       </c>
       <c r="P83" s="7" t="inlineStr">
         <is>
-          <t>cfp_closed</t>
+          <t>upcoming</t>
         </is>
       </c>
       <c r="Q83" s="7" t="inlineStr">
@@ -8389,64 +8389,64 @@
       </c>
       <c r="R83" s="7" t="inlineStr">
         <is>
-          <t>abstract deadline (extended) 2026-02-02 confirmed passed; early/advance registration deadline confirmed 2026-07-31 (upcoming)</t>
+          <t>new entry</t>
         </is>
       </c>
       <c r="S83" s="7" t="inlineStr">
         <is>
-          <t>https://appliedsuperconductivity.org/asc2026/</t>
+          <t>https://www.lso.uni-hannover.de/en/isopc; https://konferenz.uni-hannover.de/event/222/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>inphomir-school-2026</t>
+          <t>tqc-2026</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>INPHOMIR Photonics School 2026</t>
+          <t>Theory of Quantum Computation, Communication and Cryptography 2026</t>
         </is>
       </c>
       <c r="C84" s="7" t="inlineStr">
         <is>
-          <t>INPHOMIR School</t>
+          <t>TQC 2026</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>Summer School</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>photonic integrated circuits;III-V on Si</t>
+          <t>quantum communication;quantum computing hardware;quantum networking</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>Bari, Italy</t>
+          <t>Sherbrooke, QC, Canada</t>
         </is>
       </c>
       <c r="I84" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="J84" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="K84" s="7" t="inlineStr">
@@ -8456,25 +8456,25 @@
       </c>
       <c r="L84" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="M84" s="7" t="inlineStr">
         <is>
-          <t>https://inphomir.eu/inphomir-school-program/</t>
-        </is>
-      </c>
-      <c r="N84" s="6" t="n">
-        <v>4</v>
+          <t>https://tqc-conference.org/2026/</t>
+        </is>
+      </c>
+      <c r="N84" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="O84" s="7" t="inlineStr">
         <is>
-          <t>Dedicated InP/III-V photonics school for NIR/MIR applications</t>
+          <t>Theory conference for quantum communication, computation and cryptography</t>
         </is>
       </c>
       <c r="P84" s="7" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>cfp_closed</t>
         </is>
       </c>
       <c r="Q84" s="7" t="inlineStr">
@@ -8484,29 +8484,29 @@
       </c>
       <c r="R84" s="7" t="inlineStr">
         <is>
-          <t>no change</t>
+          <t>main submission deadline 2026-02-01 (AoE) and early-bird registration 2026-06-28 both confirmed passed; poster-only track closed 2026-04-20</t>
         </is>
       </c>
       <c r="S84" s="7" t="inlineStr">
         <is>
-          <t>https://inphomir.eu/inphomir-school-program/</t>
+          <t>https://tqc-conference.org/2026/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>ieee-qce26</t>
+          <t>photon-2026-iop</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>IEEE Quantum Week 2026</t>
+          <t>Photon 2026</t>
         </is>
       </c>
       <c r="C85" s="7" t="inlineStr">
         <is>
-          <t>QCE26</t>
+          <t>Photon 2026</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
@@ -8516,55 +8516,55 @@
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>quantum computing hardware;quantum communication;integrated quantum photonics</t>
+          <t>quantum optics;nonlinear optics;quantum communication</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>Toronto, ON, Canada</t>
+          <t>Newcastle upon Tyne, UK</t>
         </is>
       </c>
       <c r="I85" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
-        </is>
-      </c>
-      <c r="K85" s="7" t="inlineStr">
-        <is>
-          <t>TBA</t>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K85" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="L85" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="M85" s="7" t="inlineStr">
         <is>
-          <t>https://qce.quantum.ieee.org/2026/</t>
-        </is>
-      </c>
-      <c r="N85" s="5" t="n">
-        <v>3</v>
+          <t>https://www.photon.org.uk/</t>
+        </is>
+      </c>
+      <c r="N85" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="O85" s="7" t="inlineStr">
         <is>
-          <t>IEEE quantum week with photonic quantum computing and QKD sessions</t>
+          <t>Biennial IOP conference jointly run by the Quantum Optics, Quantum Electronics &amp; Photonics, and Quantum Information groups</t>
         </is>
       </c>
       <c r="P85" s="7" t="inlineStr">
@@ -8579,29 +8579,29 @@
       </c>
       <c r="R85" s="7" t="inlineStr">
         <is>
-          <t>technical paper submission window (Apr 13-27 2026) confirmed passed; registration opened Apr 14 2026</t>
+          <t>new entry</t>
         </is>
       </c>
       <c r="S85" s="7" t="inlineStr">
         <is>
-          <t>https://qce.quantum.ieee.org/2026/</t>
+          <t>https://www.photon.org.uk/; https://www.iop.org/events/photon-2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>photonics-switching-2026</t>
+          <t>asc-2026</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>PSC 2026 — Photonics in Switching and Computing</t>
+          <t>Applied Superconductivity Conference 2026</t>
         </is>
       </c>
       <c r="C86" s="7" t="inlineStr">
         <is>
-          <t>PSC 2026</t>
+          <t>ASC 2026</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
@@ -8611,27 +8611,27 @@
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>photonic integrated circuits;silicon photonics</t>
+          <t>SNSPDs;cryogenic electronics;single-photon sources</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>Valencia, Spain</t>
+          <t>Pittsburgh, PA, USA</t>
         </is>
       </c>
       <c r="I86" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="J86" s="7" t="inlineStr">
@@ -8639,32 +8639,32 @@
           <t>TBA</t>
         </is>
       </c>
-      <c r="K86" s="7" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="L86" s="7" t="inlineStr">
-        <is>
-          <t>TBA</t>
+      <c r="K86" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="L86" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="M86" s="7" t="inlineStr">
         <is>
-          <t>https://psc2026.org/</t>
-        </is>
-      </c>
-      <c r="N86" s="5" t="n">
-        <v>3</v>
+          <t>https://appliedsuperconductivity.org/asc2026/</t>
+        </is>
+      </c>
+      <c r="N86" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="O86" s="7" t="inlineStr">
         <is>
-          <t>Photonic switching and routing conference</t>
+          <t>Premier superconductivity conference with major SNSPD and cryogenic electronics sessions</t>
         </is>
       </c>
       <c r="P86" s="7" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>cfp_closed</t>
         </is>
       </c>
       <c r="Q86" s="7" t="inlineStr">
@@ -8674,64 +8674,64 @@
       </c>
       <c r="R86" s="7" t="inlineStr">
         <is>
-          <t>confirmed real event is PSC (Photonics in Switching and Computing) 2026; dates/location/website found</t>
+          <t>abstract deadline (extended) 2026-02-02 confirmed passed; early/advance registration deadline confirmed 2026-07-31 (upcoming)</t>
         </is>
       </c>
       <c r="S86" s="7" t="inlineStr">
         <is>
-          <t>https://psc2026.org/; https://ieeephotonics.org/event/2026-international-conference-on-photonics-in-switching-and-computing-psc/</t>
+          <t>https://appliedsuperconductivity.org/asc2026/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>ecoc-2026</t>
+          <t>inphomir-school-2026</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>European Conference on Optical Communication 2026</t>
+          <t>INPHOMIR Photonics School 2026</t>
         </is>
       </c>
       <c r="C87" s="7" t="inlineStr">
         <is>
-          <t>ECOC 2026</t>
+          <t>INPHOMIR School</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Summer School</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>photonic integrated circuits;silicon photonics;quantum communication;integrated quantum photonics</t>
+          <t>photonic integrated circuits;III-V on Si</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>Málaga, Spain</t>
+          <t>Bari, Italy</t>
         </is>
       </c>
       <c r="I87" s="7" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K87" s="7" t="inlineStr">
@@ -8741,12 +8741,12 @@
       </c>
       <c r="L87" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="M87" s="7" t="inlineStr">
         <is>
-          <t>https://ecoc2026.org/</t>
+          <t>https://inphomir.eu/inphomir-school-program/</t>
         </is>
       </c>
       <c r="N87" s="6" t="n">
@@ -8754,12 +8754,12 @@
       </c>
       <c r="O87" s="7" t="inlineStr">
         <is>
-          <t>Europe's flagship optical comms conference with quantum technologies track</t>
+          <t>Dedicated InP/III-V photonics school for NIR/MIR applications</t>
         </is>
       </c>
       <c r="P87" s="7" t="inlineStr">
         <is>
-          <t>cfp_closed</t>
+          <t>upcoming</t>
         </is>
       </c>
       <c r="Q87" s="7" t="inlineStr">
@@ -8769,29 +8769,29 @@
       </c>
       <c r="R87" s="7" t="inlineStr">
         <is>
-          <t>paper submission deadline was 2026-04-22 (now closed); confirmed Sep 20-24 Málaga</t>
+          <t>no change</t>
         </is>
       </c>
       <c r="S87" s="7" t="inlineStr">
         <is>
-          <t>https://ecoc2026.org/; https://ecoc2026.org/ECOC2026/paper-submission</t>
+          <t>https://inphomir.eu/inphomir-school-program/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>mne-2026</t>
+          <t>ieee-qce26</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>International Conference on Micro and Nano Engineering 2026</t>
+          <t>IEEE Quantum Week 2026</t>
         </is>
       </c>
       <c r="C88" s="7" t="inlineStr">
         <is>
-          <t>MNE 2026</t>
+          <t>QCE26</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
@@ -8801,22 +8801,22 @@
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>photonic integrated circuits;nanophotonics;2D-material photonics</t>
+          <t>quantum computing hardware;quantum communication;integrated quantum photonics</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>Interlaken, Switzerland</t>
+          <t>Toronto, ON, Canada</t>
         </is>
       </c>
       <c r="I88" s="7" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="J88" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="K88" s="7" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="M88" s="7" t="inlineStr">
         <is>
-          <t>https://mne2026.imnes.org/</t>
+          <t>https://qce.quantum.ieee.org/2026/</t>
         </is>
       </c>
       <c r="N88" s="5" t="n">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="O88" s="7" t="inlineStr">
         <is>
-          <t>Nanofabrication conference relevant to photonic device processing</t>
+          <t>IEEE quantum week with photonic quantum computing and QKD sessions</t>
         </is>
       </c>
       <c r="P88" s="7" t="inlineStr">
@@ -8864,29 +8864,29 @@
       </c>
       <c r="R88" s="7" t="inlineStr">
         <is>
-          <t>main CFP confirmed closed (author notifications already sent); late-breaking poster track open through end-Aug-2026</t>
+          <t>technical paper submission window (Apr 13-27 2026) confirmed passed; registration opened Apr 14 2026</t>
         </is>
       </c>
       <c r="S88" s="7" t="inlineStr">
         <is>
-          <t>https://mne2026.imnes.org/</t>
+          <t>https://qce.quantum.ieee.org/2026/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>fio-2026</t>
+          <t>photonics-switching-2026</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>Frontiers in Optics + Laser Science 2026</t>
+          <t>PSC 2026 — Photonics in Switching and Computing</t>
         </is>
       </c>
       <c r="C89" s="7" t="inlineStr">
         <is>
-          <t>FiO+LS 2026</t>
+          <t>PSC 2026</t>
         </is>
       </c>
       <c r="D89" s="7" t="inlineStr">
@@ -8896,32 +8896,32 @@
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>quantum optics;nonlinear optics;nanophotonics</t>
+          <t>photonic integrated circuits;silicon photonics</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>Rochester, NY, USA</t>
-        </is>
-      </c>
-      <c r="I89" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
-      <c r="J89" s="8" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
+          <t>Valencia, Spain</t>
+        </is>
+      </c>
+      <c r="I89" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="J89" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
         </is>
       </c>
       <c r="K89" s="7" t="inlineStr">
@@ -8929,14 +8929,14 @@
           <t>TBA</t>
         </is>
       </c>
-      <c r="L89" s="9" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
+      <c r="L89" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
         </is>
       </c>
       <c r="M89" s="7" t="inlineStr">
         <is>
-          <t>https://frontiersinoptics.com/</t>
+          <t>https://psc2026.org/</t>
         </is>
       </c>
       <c r="N89" s="5" t="n">
@@ -8944,12 +8944,12 @@
       </c>
       <c r="O89" s="7" t="inlineStr">
         <is>
-          <t>Broad US photonics conference with quantum optics tracks</t>
+          <t>Photonic switching and routing conference</t>
         </is>
       </c>
       <c r="P89" s="7" t="inlineStr">
         <is>
-          <t>cfp_open</t>
+          <t>upcoming</t>
         </is>
       </c>
       <c r="Q89" s="7" t="inlineStr">
@@ -8959,29 +8959,29 @@
       </c>
       <c r="R89" s="7" t="inlineStr">
         <is>
-          <t>CORRECTED end date to 2026-10-01 (was 2026-09-30); abstract deadline confirmed 2026-07-07 (imminent); advance registration deadline 2026-08-14</t>
+          <t>confirmed real event is PSC (Photonics in Switching and Computing) 2026; dates/location/website found</t>
         </is>
       </c>
       <c r="S89" s="7" t="inlineStr">
         <is>
-          <t>https://frontiersinoptics.com/</t>
+          <t>https://psc2026.org/; https://ieeephotonics.org/event/2026-international-conference-on-photonics-in-switching-and-computing-psc/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>les-houches-focm-2026</t>
+          <t>dpg-bad-honnef-applied-photonics-2026</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>Les Houches Doctoral Training: Frontiers of Condensed Matter</t>
+          <t>Bad Honnef Physics School: Applied Photonics</t>
         </is>
       </c>
       <c r="C90" s="7" t="inlineStr">
         <is>
-          <t>LH FOCM 2026</t>
+          <t>DPG Bad Honnef AP</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
@@ -8991,22 +8991,22 @@
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>optomechanics;nanophotonics</t>
+          <t>nanophotonics;integrated quantum photonics</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>Les Houches, France</t>
+          <t>Bad Honnef, Germany</t>
         </is>
       </c>
       <c r="I90" s="7" t="inlineStr">
@@ -9026,20 +9026,20 @@
       </c>
       <c r="L90" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="M90" s="7" t="inlineStr">
         <is>
-          <t>https://frontiers-les-houches.org/</t>
-        </is>
-      </c>
-      <c r="N90" s="5" t="n">
-        <v>3</v>
+          <t>https://www.dpg-physik.de/veranstaltungen/2026/applied_photonics</t>
+        </is>
+      </c>
+      <c r="N90" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="O90" s="7" t="inlineStr">
         <is>
-          <t>Session on strong coupling of photons with magnons/phonons/spins — adjacent to optomechanics and hybrid quantum systems</t>
+          <t>DPG physics school on photonics fundamentals incl. nanooptics/quantum photonic systems, open to PhD students</t>
         </is>
       </c>
       <c r="P90" s="7" t="inlineStr">
@@ -9059,59 +9059,59 @@
       </c>
       <c r="S90" s="7" t="inlineStr">
         <is>
-          <t>https://frontiers-les-houches.org/</t>
+          <t>https://www.dpg-physik.de/veranstaltungen/2026/applied_photonics</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>hdqs-2026</t>
+          <t>ecoc-2026</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>High-Dimensional Quantum Systems Workshop 2026</t>
+          <t>European Conference on Optical Communication 2026</t>
         </is>
       </c>
       <c r="C91" s="7" t="inlineStr">
         <is>
-          <t>HDQS 2026</t>
+          <t>ECOC 2026</t>
         </is>
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>quantum optics;quantum communication;integrated quantum photonics</t>
+          <t>photonic integrated circuits;silicon photonics;quantum communication;integrated quantum photonics</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>Benasque, Spain</t>
+          <t>Málaga, Spain</t>
         </is>
       </c>
       <c r="I91" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="K91" s="7" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="L91" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="M91" s="7" t="inlineStr">
         <is>
-          <t>https://benasque.org/2026hdqs/</t>
+          <t>https://ecoc2026.org/</t>
         </is>
       </c>
       <c r="N91" s="6" t="n">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="O91" s="7" t="inlineStr">
         <is>
-          <t>Benasque workshop on high-dimensional quantum photonics and quantum information</t>
+          <t>Europe's flagship optical comms conference with quantum technologies track</t>
         </is>
       </c>
       <c r="P91" s="7" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>cfp_closed</t>
         </is>
       </c>
       <c r="Q91" s="7" t="inlineStr">
@@ -9149,29 +9149,29 @@
       </c>
       <c r="R91" s="7" t="inlineStr">
         <is>
-          <t>web search returned contradictory/unsourced date claims for this run; kept prior dates pending manual re-check of benasque.org/2026hdqs/</t>
+          <t>paper submission deadline was 2026-04-22 (now closed); confirmed Sep 20-24 Málaga</t>
         </is>
       </c>
       <c r="S91" s="7" t="inlineStr">
         <is>
-          <t>https://benasque.org/2026hdqs/</t>
+          <t>https://ecoc2026.org/; https://ecoc2026.org/ECOC2026/paper-submission</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>photonics-days-2026</t>
+          <t>mne-2026</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>Photonics Days Berlin 2026</t>
+          <t>International Conference on Micro and Nano Engineering 2026</t>
         </is>
       </c>
       <c r="C92" s="7" t="inlineStr">
         <is>
-          <t>PDB 2026</t>
+          <t>MNE 2026</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
@@ -9181,22 +9181,22 @@
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>integrated quantum photonics;photonic integrated circuits;nanophotonics</t>
+          <t>photonic integrated circuits;nanophotonics;2D-material photonics</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>Berlin, Germany</t>
+          <t>Interlaken, Switzerland</t>
         </is>
       </c>
       <c r="I92" s="7" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="M92" s="7" t="inlineStr">
         <is>
-          <t>https://photonic-days-berlin.com/</t>
+          <t>https://mne2026.imnes.org/</t>
         </is>
       </c>
       <c r="N92" s="5" t="n">
@@ -9229,12 +9229,12 @@
       </c>
       <c r="O92" s="7" t="inlineStr">
         <is>
-          <t>German photonics industry and research meeting</t>
+          <t>Nanofabrication conference relevant to photonic device processing</t>
         </is>
       </c>
       <c r="P92" s="7" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>cfp_closed</t>
         </is>
       </c>
       <c r="Q92" s="7" t="inlineStr">
@@ -9244,64 +9244,64 @@
       </c>
       <c r="R92" s="7" t="inlineStr">
         <is>
-          <t>dates/venue corroborated by 3 independent sources (WISTA Event Center, Adlershof); appears to be invited-speaker/exhibition event with no open CFP</t>
+          <t>main CFP confirmed closed (author notifications already sent); late-breaking poster track open through end-Aug-2026</t>
         </is>
       </c>
       <c r="S92" s="7" t="inlineStr">
         <is>
-          <t>https://photonic-days-berlin.com/</t>
+          <t>https://mne2026.imnes.org/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>it-fab-school-2026</t>
+          <t>fio-2026</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>It-fab Italian Network for Micro and Nano Fabrication School 2026</t>
+          <t>Frontiers in Optics + Laser Science 2026</t>
         </is>
       </c>
       <c r="C93" s="7" t="inlineStr">
         <is>
-          <t>It-fab School 2026</t>
+          <t>FiO+LS 2026</t>
         </is>
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>Summer School</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>photonic integrated circuits;nanophotonics</t>
+          <t>quantum optics;nonlinear optics;nanophotonics</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>2026-10-27</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>2026-10-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>Turin (INRiM), Italy</t>
-        </is>
-      </c>
-      <c r="I93" s="7" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="J93" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
+          <t>Rochester, NY, USA</t>
+        </is>
+      </c>
+      <c r="I93" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="J93" s="8" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="K93" s="7" t="inlineStr">
@@ -9309,14 +9309,14 @@
           <t>TBA</t>
         </is>
       </c>
-      <c r="L93" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
+      <c r="L93" s="9" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="M93" s="7" t="inlineStr">
         <is>
-          <t>https://itfab.bo.imm.cnr.it/</t>
+          <t>https://frontiersinoptics.com/</t>
         </is>
       </c>
       <c r="N93" s="5" t="n">
@@ -9324,12 +9324,12 @@
       </c>
       <c r="O93" s="7" t="inlineStr">
         <is>
-          <t>Italian nanofabrication school relevant to photonic device processing</t>
+          <t>Broad US photonics conference with quantum optics tracks</t>
         </is>
       </c>
       <c r="P93" s="7" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>cfp_open</t>
         </is>
       </c>
       <c r="Q93" s="7" t="inlineStr">
@@ -9339,54 +9339,54 @@
       </c>
       <c r="R93" s="7" t="inlineStr">
         <is>
-          <t>confirmed real dates/location: Oct 27-30 2026, Turin (INRiM/STMicroelectronics), first 'traveling' edition</t>
+          <t>CORRECTED end date to 2026-10-01 (was 2026-09-30); abstract deadline confirmed 2026-07-07 (imminent); advance registration deadline 2026-08-14</t>
         </is>
       </c>
       <c r="S93" s="7" t="inlineStr">
         <is>
-          <t>https://itfab.bo.imm.cnr.it/; https://www.inrim.it/it/eventi/it-fab-hands-school-micro-and-nano-fabrication</t>
+          <t>https://frontiersinoptics.com/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>ipc-2026</t>
+          <t>les-houches-focm-2026</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>IEEE Photonics Conference 2026</t>
+          <t>Les Houches Doctoral Training: Frontiers of Condensed Matter</t>
         </is>
       </c>
       <c r="C94" s="7" t="inlineStr">
         <is>
-          <t>IPC 2026</t>
+          <t>LH FOCM 2026</t>
         </is>
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Summer School</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>integrated quantum photonics;photonic integrated circuits;silicon photonics</t>
+          <t>optomechanics;nanophotonics</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>2026-11-08</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>2026-11-12</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>Denver, CO, USA</t>
+          <t>Les Houches, France</t>
         </is>
       </c>
       <c r="I94" s="7" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="J94" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K94" s="7" t="inlineStr">
@@ -9406,25 +9406,25 @@
       </c>
       <c r="L94" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="M94" s="7" t="inlineStr">
         <is>
-          <t>https://ieee-ipc.org/</t>
-        </is>
-      </c>
-      <c r="N94" s="6" t="n">
-        <v>4</v>
+          <t>https://frontiers-les-houches.org/</t>
+        </is>
+      </c>
+      <c r="N94" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="O94" s="7" t="inlineStr">
         <is>
-          <t>IEEE flagship photonics devices and integrated systems conference</t>
+          <t>Session on strong coupling of photons with magnons/phonons/spins — adjacent to optomechanics and hybrid quantum systems</t>
         </is>
       </c>
       <c r="P94" s="7" t="inlineStr">
         <is>
-          <t>cfp_closed</t>
+          <t>upcoming</t>
         </is>
       </c>
       <c r="Q94" s="7" t="inlineStr">
@@ -9434,29 +9434,29 @@
       </c>
       <c r="R94" s="7" t="inlineStr">
         <is>
-          <t>two-stage submission (abstract ~Jan/paper ~Mar-Apr 2026) confirmed already passed</t>
+          <t>new entry</t>
         </is>
       </c>
       <c r="S94" s="7" t="inlineStr">
         <is>
-          <t>https://ieee-ipc.org/</t>
+          <t>https://frontiers-les-houches.org/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>eqtc-2026</t>
+          <t>qps-paderborn-2026</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>European Quantum Technologies Conference 2026</t>
+          <t>Quantum Photonics Spotlight 2026</t>
         </is>
       </c>
       <c r="C95" s="7" t="inlineStr">
         <is>
-          <t>EQTC 2026</t>
+          <t>QPS2026</t>
         </is>
       </c>
       <c r="D95" s="7" t="inlineStr">
@@ -9466,32 +9466,32 @@
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>integrated quantum photonics;quantum communication;quantum computing hardware;quantum networking</t>
+          <t>integrated quantum photonics;quantum communication;quantum computing hardware</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>2026-11-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>2026-12-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>Dublin, Ireland</t>
-        </is>
-      </c>
-      <c r="I95" s="9" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
+          <t>Paderborn, Germany</t>
+        </is>
+      </c>
+      <c r="I95" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
         </is>
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K95" s="7" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="M95" s="7" t="inlineStr">
         <is>
-          <t>https://www.eqtc2026.eu/</t>
+          <t>https://phoqs.uni-paderborn.de/en/veranstaltungen/quantum-photonics-spotlight-2026</t>
         </is>
       </c>
       <c r="N95" s="4" t="n">
@@ -9514,12 +9514,12 @@
       </c>
       <c r="O95" s="7" t="inlineStr">
         <is>
-          <t>EU Quantum Flagship conference — all aspects of quantum technology, high visibility</t>
+          <t>Dedicated German quantum-photonics conference hosted by Paderborn's PhoQS institute — direct core-topic overlap, low travel cost</t>
         </is>
       </c>
       <c r="P95" s="7" t="inlineStr">
         <is>
-          <t>cfp_open</t>
+          <t>upcoming</t>
         </is>
       </c>
       <c r="Q95" s="7" t="inlineStr">
@@ -9529,64 +9529,64 @@
       </c>
       <c r="R95" s="7" t="inlineStr">
         <is>
-          <t>Science &amp; Technology track abstract deadline confirmed 2026-07-20 (notification ~Aug 14); updated to dedicated conference site eqtc2026.eu</t>
+          <t>new entry</t>
         </is>
       </c>
       <c r="S95" s="7" t="inlineStr">
         <is>
-          <t>https://www.eqtc2026.eu/; https://qt.eu/events/eqtc-2026-european-quantum-technologies-conference</t>
+          <t>https://phoqs.uni-paderborn.de/en/veranstaltungen/quantum-photonics-spotlight-2026</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>photonics-west-2027</t>
+          <t>hdqs-2026</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>SPIE Photonics West 2027</t>
+          <t>High-Dimensional Quantum Systems Workshop 2026</t>
         </is>
       </c>
       <c r="C96" s="7" t="inlineStr">
         <is>
-          <t>PW 2027</t>
+          <t>HDQS 2026</t>
         </is>
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>integrated quantum photonics;silicon photonics;nonlinear optics;single-photon sources</t>
+          <t>quantum optics;quantum communication;integrated quantum photonics</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>2027-01-30</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>2027-02-04</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>San Francisco, CA, USA</t>
-        </is>
-      </c>
-      <c r="I96" s="9" t="inlineStr">
-        <is>
-          <t>2026-07-22</t>
+          <t>Benasque, Spain</t>
+        </is>
+      </c>
+      <c r="I96" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
         </is>
       </c>
       <c r="J96" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K96" s="7" t="inlineStr">
@@ -9596,25 +9596,25 @@
       </c>
       <c r="L96" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="M96" s="7" t="inlineStr">
         <is>
-          <t>https://spie.org/conferences-and-exhibitions/photonics-west</t>
-        </is>
-      </c>
-      <c r="N96" s="4" t="n">
-        <v>5</v>
+          <t>https://benasque.org/2026hdqs/</t>
+        </is>
+      </c>
+      <c r="N96" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="O96" s="7" t="inlineStr">
         <is>
-          <t>SPIE flagship with Quantum West and Si-photonics tracks — abstract deadline Jul 22 2026</t>
+          <t>Benasque workshop on high-dimensional quantum photonics and quantum information</t>
         </is>
       </c>
       <c r="P96" s="7" t="inlineStr">
         <is>
-          <t>cfp_open</t>
+          <t>upcoming</t>
         </is>
       </c>
       <c r="Q96" s="7" t="inlineStr">
@@ -9624,29 +9624,29 @@
       </c>
       <c r="R96" s="7" t="inlineStr">
         <is>
-          <t>abstract deadline 2026-07-22 reconfirmed unchanged and still open</t>
+          <t>web search returned contradictory/unsourced date claims for this run; kept prior dates pending manual re-check of benasque.org/2026hdqs/</t>
         </is>
       </c>
       <c r="S96" s="7" t="inlineStr">
         <is>
-          <t>https://spie.org/conferences-and-exhibitions/photonics-west; https://spie.org/conferences-and-exhibitions/photonics-west/program/browse-program</t>
+          <t>https://benasque.org/2026hdqs/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>qip-2027</t>
+          <t>nanop-2026</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>30th Quantum Information Processing Conference</t>
+          <t>NANOP 2026 — 8th Nanophotonics and Micro/Nano Optics International Conference</t>
         </is>
       </c>
       <c r="C97" s="7" t="inlineStr">
         <is>
-          <t>QIP 2027</t>
+          <t>NANOP 2026</t>
         </is>
       </c>
       <c r="D97" s="7" t="inlineStr">
@@ -9656,22 +9656,22 @@
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>quantum communication;quantum computing hardware;quantum networking</t>
+          <t>nanophotonics;optomechanics</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>2027-02-20</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>2027-02-26</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Rome, Italy</t>
         </is>
       </c>
       <c r="I97" s="7" t="inlineStr">
@@ -9681,12 +9681,12 @@
       </c>
       <c r="J97" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="K97" s="7" t="inlineStr">
-        <is>
-          <t>TBA</t>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K97" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="L97" s="7" t="inlineStr">
@@ -9696,20 +9696,20 @@
       </c>
       <c r="M97" s="7" t="inlineStr">
         <is>
-          <t>https://qipconference.org/2027/</t>
-        </is>
-      </c>
-      <c r="N97" s="6" t="n">
-        <v>4</v>
+          <t>https://premc.org/conferences/nanop-nanophotonics-micro-nano-optics/</t>
+        </is>
+      </c>
+      <c r="N97" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="O97" s="7" t="inlineStr">
         <is>
-          <t>Premier annual quantum information conference; quantum networking and hardware sessions</t>
+          <t>Established nanophotonics conference series covering nano-optomechanics and functional nanophotonics</t>
         </is>
       </c>
       <c r="P97" s="7" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>cfp_open</t>
         </is>
       </c>
       <c r="Q97" s="7" t="inlineStr">
@@ -9719,29 +9719,29 @@
       </c>
       <c r="R97" s="7" t="inlineStr">
         <is>
-          <t>dates/venue reconfirmed unchanged; CFP/deadlines not yet announced, expected ~Sep-Oct 2026</t>
+          <t>new entry</t>
         </is>
       </c>
       <c r="S97" s="7" t="inlineStr">
         <is>
-          <t>https://qipconference.org/2027/; https://qip.iaqi.org/nextqip</t>
+          <t>https://premc.org/conferences/nanop-nanophotonics-micro-nano-optics/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>dpg-samop-2027</t>
+          <t>photonics-days-2026</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>DPG Frühjahrstagung SAMOP 2027</t>
+          <t>Photonics Days Berlin 2026</t>
         </is>
       </c>
       <c r="C98" s="7" t="inlineStr">
         <is>
-          <t>DPG SAMOP 2027</t>
+          <t>PDB 2026</t>
         </is>
       </c>
       <c r="D98" s="7" t="inlineStr">
@@ -9751,22 +9751,22 @@
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>quantum optics;nanophotonics;integrated quantum photonics</t>
+          <t>integrated quantum photonics;photonic integrated circuits;nanophotonics</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>2027-02-28</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>2027-03-05</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>Hannover, Germany</t>
+          <t>Berlin, Germany</t>
         </is>
       </c>
       <c r="I98" s="7" t="inlineStr">
@@ -9791,15 +9791,15 @@
       </c>
       <c r="M98" s="7" t="inlineStr">
         <is>
-          <t>https://www.dpg-physik.de/veranstaltungen/2027/dpg-fruehjahrstagung-hannover</t>
-        </is>
-      </c>
-      <c r="N98" s="6" t="n">
-        <v>4</v>
+          <t>https://photonic-days-berlin.com/</t>
+        </is>
+      </c>
+      <c r="N98" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="O98" s="7" t="inlineStr">
         <is>
-          <t>DPG spring meeting for quantum optics and photonics — easily accessible from Münster</t>
+          <t>German photonics industry and research meeting</t>
         </is>
       </c>
       <c r="P98" s="7" t="inlineStr">
@@ -9814,54 +9814,54 @@
       </c>
       <c r="R98" s="7" t="inlineStr">
         <is>
-          <t>dates reconfirmed unchanged; updated to specific DPG event page (dedicated hannover-conference microsite not yet live, expected ~Sep 2026); an ambiguous/unverified cancellation signal was found in secondary search snippets — flagged for manual re-check, not acted on</t>
+          <t>dates/venue corroborated by 3 independent sources (WISTA Event Center, Adlershof); appears to be invited-speaker/exhibition event with no open CFP</t>
         </is>
       </c>
       <c r="S98" s="7" t="inlineStr">
         <is>
-          <t>https://dpg-physik.de/</t>
+          <t>https://photonic-days-berlin.com/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>ofc-2027</t>
+          <t>quest-cryo-2026</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>Optical Fiber Communication Conference 2027</t>
+          <t>QUEST 2026 — 2nd International Workshop on Quantum, Cryogenic and Superconductive Computing</t>
         </is>
       </c>
       <c r="C99" s="7" t="inlineStr">
         <is>
-          <t>OFC 2027</t>
+          <t>QUEST 2026</t>
         </is>
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>photonic integrated circuits;silicon photonics;quantum communication</t>
+          <t>cryogenic electronics;quantum computing hardware;SNSPDs</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>2027-03-07</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>2027-03-11</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, USA</t>
+          <t>Niigata, Japan</t>
         </is>
       </c>
       <c r="I99" s="7" t="inlineStr">
@@ -9886,20 +9886,20 @@
       </c>
       <c r="M99" s="7" t="inlineStr">
         <is>
-          <t>https://ofcconference.org/</t>
-        </is>
-      </c>
-      <c r="N99" s="6" t="n">
-        <v>4</v>
+          <t>https://ieeecsc.org/event/workshop/quantum-cryogenic-superconductive-computing-2026</t>
+        </is>
+      </c>
+      <c r="N99" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="O99" s="7" t="inlineStr">
         <is>
-          <t>World's largest optical comms conference with PIC and quantum networking sessions</t>
+          <t>Co-organized by German Leibniz Institutes IPHT Jena and IHP; covers cryogenic electronics relevant to SNSPD/quantum-hardware readout</t>
         </is>
       </c>
       <c r="P99" s="7" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>cfp_open</t>
         </is>
       </c>
       <c r="Q99" s="7" t="inlineStr">
@@ -9909,29 +9909,29 @@
       </c>
       <c r="R99" s="7" t="inlineStr">
         <is>
-          <t>dates/venue reconfirmed unchanged; deadlines not yet published</t>
+          <t>new entry</t>
         </is>
       </c>
       <c r="S99" s="7" t="inlineStr">
         <is>
-          <t>https://ofcconference.org/</t>
+          <t>https://ieeecsc.org/event/workshop/quantum-cryogenic-superconductive-computing-2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>les-houches-photonics-ai-2027</t>
+          <t>it-fab-school-2026</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>Les Houches School: Photonics and Artificial Intelligence</t>
+          <t>It-fab Italian Network for Micro and Nano Fabrication School 2026</t>
         </is>
       </c>
       <c r="C100" s="7" t="inlineStr">
         <is>
-          <t>LH Photonics-AI 2027</t>
+          <t>It-fab School 2026</t>
         </is>
       </c>
       <c r="D100" s="7" t="inlineStr">
@@ -9946,17 +9946,17 @@
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>2027-04-04</t>
+          <t>2026-10-27</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>2027-04-09</t>
+          <t>2026-10-30</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>Les Houches, France</t>
+          <t>Turin (INRiM), Italy</t>
         </is>
       </c>
       <c r="I100" s="7" t="inlineStr">
@@ -9981,15 +9981,15 @@
       </c>
       <c r="M100" s="7" t="inlineStr">
         <is>
-          <t>https://www.houches-school-physics.com/program/program-2027/</t>
-        </is>
-      </c>
-      <c r="N100" s="4" t="n">
-        <v>5</v>
+          <t>https://itfab.bo.imm.cnr.it/</t>
+        </is>
+      </c>
+      <c r="N100" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="O100" s="7" t="inlineStr">
         <is>
-          <t>New 2027 Les Houches thematic school on integrated photonics and AI-assisted photonic design (organizers incl. C2N, FEMTO-ST)</t>
+          <t>Italian nanofabrication school relevant to photonic device processing</t>
         </is>
       </c>
       <c r="P100" s="7" t="inlineStr">
@@ -10004,29 +10004,29 @@
       </c>
       <c r="R100" s="7" t="inlineStr">
         <is>
-          <t>new entry</t>
+          <t>confirmed real dates/location: Oct 27-30 2026, Turin (INRiM/STMicroelectronics), first 'traveling' edition</t>
         </is>
       </c>
       <c r="S100" s="7" t="inlineStr">
         <is>
-          <t>https://www.sfoptique.org/pages/sfo/ecoles-thematiques/2027-artificial-intelligence-photonics/2027-photonics-artificial-intelligence.html</t>
+          <t>https://itfab.bo.imm.cnr.it/; https://www.inrim.it/it/eventi/it-fab-hands-school-micro-and-nano-fabrication</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>spie-oo-2027</t>
+          <t>ipc-2026</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>SPIE Optics + Optoelectronics 2027</t>
+          <t>IEEE Photonics Conference 2026</t>
         </is>
       </c>
       <c r="C101" s="7" t="inlineStr">
         <is>
-          <t>SPIE O+O 2027</t>
+          <t>IPC 2026</t>
         </is>
       </c>
       <c r="D101" s="7" t="inlineStr">
@@ -10036,22 +10036,22 @@
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>integrated quantum photonics;quantum optics;nanophotonics</t>
+          <t>integrated quantum photonics;photonic integrated circuits;silicon photonics</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>2027-04-05</t>
+          <t>2026-11-08</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>2027-04-08</t>
+          <t>2026-11-12</t>
         </is>
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>Prague, Czech Republic</t>
+          <t>Denver, CO, USA</t>
         </is>
       </c>
       <c r="I101" s="7" t="inlineStr">
@@ -10076,7 +10076,7 @@
       </c>
       <c r="M101" s="7" t="inlineStr">
         <is>
-          <t>https://spie.org/conferences-and-exhibitions/optics-and-optoelectronics</t>
+          <t>https://ieee-ipc.org/</t>
         </is>
       </c>
       <c r="N101" s="6" t="n">
@@ -10084,12 +10084,12 @@
       </c>
       <c r="O101" s="7" t="inlineStr">
         <is>
-          <t>SPIE European conference with quantum photonics and nanophotonics tracks</t>
+          <t>IEEE flagship photonics devices and integrated systems conference</t>
         </is>
       </c>
       <c r="P101" s="7" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>cfp_closed</t>
         </is>
       </c>
       <c r="Q101" s="7" t="inlineStr">
@@ -10099,29 +10099,29 @@
       </c>
       <c r="R101" s="7" t="inlineStr">
         <is>
-          <t>official website confirmed: spie.org/conferences-and-exhibitions/optics-and-optoelectronics (was unknown/TBA on file)</t>
+          <t>two-stage submission (abstract ~Jan/paper ~Mar-Apr 2026) confirmed already passed</t>
         </is>
       </c>
       <c r="S101" s="7" t="inlineStr">
         <is>
-          <t>original list</t>
+          <t>https://ieee-ipc.org/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>aps-summit-2027</t>
+          <t>sensing-quantum-light-2026</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>APS Global Physics Summit 2027</t>
+          <t>Sensing with Quantum Light 2026</t>
         </is>
       </c>
       <c r="C102" s="7" t="inlineStr">
         <is>
-          <t>APS Summit 2027</t>
+          <t>SQL26</t>
         </is>
       </c>
       <c r="D102" s="7" t="inlineStr">
@@ -10131,22 +10131,22 @@
       </c>
       <c r="E102" s="7" t="inlineStr">
         <is>
-          <t>quantum optics;quantum computing hardware;integrated quantum photonics</t>
+          <t>quantum optics;squeezed light;nonlinear optics</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>2027-04-11</t>
+          <t>2026-11-09</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>2027-04-16</t>
+          <t>2026-11-13</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, USA</t>
+          <t>Cologne, Germany</t>
         </is>
       </c>
       <c r="I102" s="7" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="J102" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K102" s="7" t="inlineStr">
@@ -10171,15 +10171,15 @@
       </c>
       <c r="M102" s="7" t="inlineStr">
         <is>
-          <t>https://www.aps.org/events/2027/summit</t>
-        </is>
-      </c>
-      <c r="N102" s="6" t="n">
-        <v>4</v>
+          <t>https://www.sqlkonferenz.com/</t>
+        </is>
+      </c>
+      <c r="N102" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="O102" s="7" t="inlineStr">
         <is>
-          <t>Joint APS March+April meeting; major quantum photonics and computing sessions</t>
+          <t>Dedicated conference on quantum-light sensing incl. squeezed light and nonlinear interferometry — bullseye for quantum optics interests</t>
         </is>
       </c>
       <c r="P102" s="7" t="inlineStr">
@@ -10194,29 +10194,29 @@
       </c>
       <c r="R102" s="7" t="inlineStr">
         <is>
-          <t>dates/venue reconfirmed unchanged; deadlines not yet published</t>
+          <t>new entry</t>
         </is>
       </c>
       <c r="S102" s="7" t="inlineStr">
         <is>
-          <t>https://www.aps.org/events/2027/summit</t>
+          <t>https://www.sqlkonferenz.com/</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>pic-international-2027</t>
+          <t>eqtc-2026</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>PIC International 2027</t>
+          <t>European Quantum Technologies Conference 2026</t>
         </is>
       </c>
       <c r="C103" s="7" t="inlineStr">
         <is>
-          <t>PIC International</t>
+          <t>EQTC 2026</t>
         </is>
       </c>
       <c r="D103" s="7" t="inlineStr">
@@ -10226,32 +10226,32 @@
       </c>
       <c r="E103" s="7" t="inlineStr">
         <is>
-          <t>photonic integrated circuits;silicon photonics</t>
+          <t>integrated quantum photonics;quantum communication;quantum computing hardware;quantum networking</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>2027-04-12</t>
+          <t>2026-11-29</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>2027-04-14</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>Brussels, Belgium</t>
-        </is>
-      </c>
-      <c r="I103" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
+          <t>Dublin, Ireland</t>
+        </is>
+      </c>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="J103" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="K103" s="7" t="inlineStr">
@@ -10266,20 +10266,20 @@
       </c>
       <c r="M103" s="7" t="inlineStr">
         <is>
-          <t>https://picinternational.net/</t>
-        </is>
-      </c>
-      <c r="N103" s="6" t="n">
-        <v>4</v>
+          <t>https://www.eqtc2026.eu/</t>
+        </is>
+      </c>
+      <c r="N103" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="O103" s="7" t="inlineStr">
         <is>
-          <t>12th edition of the PIC industry conference; useful for PIC industry contacts</t>
+          <t>EU Quantum Flagship conference — all aspects of quantum technology, high visibility</t>
         </is>
       </c>
       <c r="P103" s="7" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>cfp_open</t>
         </is>
       </c>
       <c r="Q103" s="7" t="inlineStr">
@@ -10289,29 +10289,29 @@
       </c>
       <c r="R103" s="7" t="inlineStr">
         <is>
-          <t>new entry</t>
+          <t>Science &amp; Technology track abstract deadline confirmed 2026-07-20 (notification ~Aug 14); updated to dedicated conference site eqtc2026.eu</t>
         </is>
       </c>
       <c r="S103" s="7" t="inlineStr">
         <is>
-          <t>https://picinternational.net/; https://10times.com/pic-international-conference</t>
+          <t>https://www.eqtc2026.eu/; https://qt.eu/events/eqtc-2026-european-quantum-technologies-conference</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>cleo-2027</t>
+          <t>photonics-west-2027</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>Conference on Lasers and Electro-Optics 2027</t>
+          <t>SPIE Photonics West 2027</t>
         </is>
       </c>
       <c r="C104" s="7" t="inlineStr">
         <is>
-          <t>CLEO 2027</t>
+          <t>PW 2027</t>
         </is>
       </c>
       <c r="D104" s="7" t="inlineStr">
@@ -10321,32 +10321,32 @@
       </c>
       <c r="E104" s="7" t="inlineStr">
         <is>
-          <t>integrated quantum photonics;quantum optics;nonlinear optics;silicon photonics;single-photon sources</t>
+          <t>integrated quantum photonics;silicon photonics;nonlinear optics;single-photon sources</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>2027-05-02</t>
+          <t>2027-01-30</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>2027-05-06</t>
+          <t>2027-02-04</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>Long Beach, CA, USA</t>
-        </is>
-      </c>
-      <c r="I104" s="7" t="inlineStr">
-        <is>
-          <t>TBA</t>
+          <t>San Francisco, CA, USA</t>
+        </is>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="J104" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="K104" s="7" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="M104" s="7" t="inlineStr">
         <is>
-          <t>https://cleoconference.org/</t>
+          <t>https://spie.org/conferences-and-exhibitions/photonics-west</t>
         </is>
       </c>
       <c r="N104" s="4" t="n">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O104" s="7" t="inlineStr">
         <is>
-          <t>Premier US laser/photonics conference; major IQP, Si-PIC and quantum optics sessions</t>
+          <t>SPIE flagship with Quantum West and Si-photonics tracks — abstract deadline Jul 22 2026</t>
         </is>
       </c>
       <c r="P104" s="7" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>cfp_open</t>
         </is>
       </c>
       <c r="Q104" s="7" t="inlineStr">
@@ -10384,54 +10384,54 @@
       </c>
       <c r="R104" s="7" t="inlineStr">
         <is>
-          <t>new entry; year roll-over from 2026 edition (Charlotte)</t>
+          <t>abstract deadline 2026-07-22 reconfirmed unchanged and still open</t>
         </is>
       </c>
       <c r="S104" s="7" t="inlineStr">
         <is>
-          <t>https://cleoconference.org/; https://www.optica.org/events/global_calendar/events/2027/conference_on_lasers_and_electro-optics_(1)/</t>
+          <t>https://spie.org/conferences-and-exhibitions/photonics-west; https://spie.org/conferences-and-exhibitions/photonics-west/program/browse-program</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>ccw-amsterdam-2027</t>
+          <t>we-heraeus-quantum-entanglement-2027</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>Critical Communications World Amsterdam 2027</t>
+          <t>879th WE-Heraeus-Seminar: Quantum Entanglement — New Concepts and Opportunities</t>
         </is>
       </c>
       <c r="C105" s="7" t="inlineStr">
         <is>
-          <t>CCW 2027</t>
+          <t>WEH-879</t>
         </is>
       </c>
       <c r="D105" s="7" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Seminar</t>
         </is>
       </c>
       <c r="E105" s="7" t="inlineStr">
         <is>
-          <t>quantum communication;quantum networking</t>
+          <t>quantum optics;quantum communication</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>2027-05-11</t>
+          <t>2027-02-14</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>2027-05-13</t>
+          <t>2027-02-17</t>
         </is>
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
-          <t>Amsterdam, Netherlands</t>
+          <t>Bad Honnef, Germany</t>
         </is>
       </c>
       <c r="I105" s="7" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="J105" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K105" s="7" t="inlineStr">
@@ -10456,15 +10456,15 @@
       </c>
       <c r="M105" s="7" t="inlineStr">
         <is>
-          <t>https://www.critical-communications-world.com/</t>
-        </is>
-      </c>
-      <c r="N105" s="3" t="n">
-        <v>2</v>
+          <t>https://www.we-heraeus-stiftung.de/veranstaltungen/quantum-entanglement-new-concepts-and-opportunities</t>
+        </is>
+      </c>
+      <c r="N105" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="O105" s="7" t="inlineStr">
         <is>
-          <t>Critical comms industry event; QKD sessions of marginal relevance</t>
+          <t>Small WE-Heraeus seminar covering entanglement implementations incl. photonic-platform experiments</t>
         </is>
       </c>
       <c r="P105" s="7" t="inlineStr">
@@ -10479,29 +10479,29 @@
       </c>
       <c r="R105" s="7" t="inlineStr">
         <is>
-          <t>new entry; year roll-over; confirmed via organizer's exhibitor page</t>
+          <t>new entry</t>
         </is>
       </c>
       <c r="S105" s="7" t="inlineStr">
         <is>
-          <t>https://www.critical-communications-world.com/exhibit-at-ccw</t>
+          <t>https://www.we-heraeus-stiftung.de/veranstaltungen/quantum-entanglement-new-concepts-and-opportunities</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>quantum-tech-world-2027</t>
+          <t>qip-2027</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>Quantum.Tech World 2027</t>
+          <t>30th Quantum Information Processing Conference</t>
         </is>
       </c>
       <c r="C106" s="7" t="inlineStr">
         <is>
-          <t>Q.Tech World 2027</t>
+          <t>QIP 2027</t>
         </is>
       </c>
       <c r="D106" s="7" t="inlineStr">
@@ -10511,22 +10511,22 @@
       </c>
       <c r="E106" s="7" t="inlineStr">
         <is>
-          <t>quantum computing hardware;quantum communication;integrated quantum photonics</t>
+          <t>quantum communication;quantum computing hardware;quantum networking</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>2027-05-25</t>
+          <t>2027-02-20</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>2027-05-26</t>
+          <t>2027-02-26</t>
         </is>
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
-          <t>Boston, MA, USA</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I106" s="7" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="J106" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="K106" s="7" t="inlineStr">
@@ -10551,15 +10551,15 @@
       </c>
       <c r="M106" s="7" t="inlineStr">
         <is>
-          <t>https://www.alphaevents.com/events-quantumtechus</t>
-        </is>
-      </c>
-      <c r="N106" s="3" t="n">
-        <v>2</v>
+          <t>https://qipconference.org/2027/</t>
+        </is>
+      </c>
+      <c r="N106" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="O106" s="7" t="inlineStr">
         <is>
-          <t>Industry quantum technology event; limited deep-science content</t>
+          <t>Premier annual quantum information conference; quantum networking and hardware sessions</t>
         </is>
       </c>
       <c r="P106" s="7" t="inlineStr">
@@ -10574,64 +10574,64 @@
       </c>
       <c r="R106" s="7" t="inlineStr">
         <is>
-          <t>new entry; year roll-over; 8th edition, Encore Boston Harbor, first year co-located with Compute.Tech</t>
+          <t>dates/venue reconfirmed unchanged; CFP/deadlines not yet announced, expected ~Sep-Oct 2026</t>
         </is>
       </c>
       <c r="S106" s="7" t="inlineStr">
         <is>
-          <t>https://www.alphaevents.com/events-quantumtechus</t>
+          <t>https://qipconference.org/2027/; https://qip.iaqi.org/nextqip</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>cleo-europe-2027</t>
+          <t>photoptics-nanoplasmeta-2027</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>CLEO/Europe-EQEC 2027</t>
+          <t>PHOTOPTICS 2027 Workshop on Nanophotonics, Plasmonics and Metamaterials</t>
         </is>
       </c>
       <c r="C107" s="7" t="inlineStr">
         <is>
-          <t>CLEO/Europe 2027</t>
+          <t>NanoPlasMeta 2027</t>
         </is>
       </c>
       <c r="D107" s="7" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="E107" s="7" t="inlineStr">
         <is>
-          <t>integrated quantum photonics;quantum optics;nonlinear optics;nanophotonics</t>
+          <t>nanophotonics;plasmonics</t>
         </is>
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>2027-06-20</t>
+          <t>2027-02-25</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
         <is>
-          <t>2027-06-25</t>
+          <t>2027-02-27</t>
         </is>
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
-          <t>Munich, Germany</t>
+          <t>Valletta, Malta</t>
         </is>
       </c>
       <c r="I107" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J107" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2026-12-03</t>
         </is>
       </c>
       <c r="K107" s="7" t="inlineStr">
@@ -10646,20 +10646,20 @@
       </c>
       <c r="M107" s="7" t="inlineStr">
         <is>
-          <t>https://cleoeurope.org/</t>
-        </is>
-      </c>
-      <c r="N107" s="4" t="n">
-        <v>5</v>
+          <t>https://photoptics.scitevents.org/</t>
+        </is>
+      </c>
+      <c r="N107" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="O107" s="7" t="inlineStr">
         <is>
-          <t>Flagship European photonics and quantum optics biennial conference</t>
+          <t>Workshop co-located with PHOTOPTICS specifically on nanophotonics/plasmonics/metamaterials</t>
         </is>
       </c>
       <c r="P107" s="7" t="inlineStr">
         <is>
-          <t>upcoming</t>
+          <t>cfp_open</t>
         </is>
       </c>
       <c r="Q107" s="7" t="inlineStr">
@@ -10669,29 +10669,29 @@
       </c>
       <c r="R107" s="7" t="inlineStr">
         <is>
-          <t>dates/venue reconfirmed unchanged via World of Photonics Congress page; abstract deadline not yet announced (2025 cycle's was late Jan)</t>
+          <t>new entry</t>
         </is>
       </c>
       <c r="S107" s="7" t="inlineStr">
         <is>
-          <t>https://cleoeurope.org/; https://www.photonics-congress.com/en/about/conferences/cleo-eqec/</t>
+          <t>https://photoptics.scitevents.org/NanoPlasMeta.aspx</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>grc-quantum-sensing-2027</t>
+          <t>dpg-samop-2027</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>Gordon Research Conference — Quantum Sensing 2027</t>
+          <t>DPG Frühjahrstagung SAMOP 2027</t>
         </is>
       </c>
       <c r="C108" s="7" t="inlineStr">
         <is>
-          <t>GRC QSe 2027</t>
+          <t>DPG SAMOP 2027</t>
         </is>
       </c>
       <c r="D108" s="7" t="inlineStr">
@@ -10701,55 +10701,55 @@
       </c>
       <c r="E108" s="7" t="inlineStr">
         <is>
-          <t>quantum optics;single-photon sources;quantum computing hardware</t>
+          <t>quantum optics;nanophotonics;integrated quantum photonics</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>2027-07-11</t>
+          <t>2027-02-28</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>2027-07-16</t>
+          <t>2027-03-05</t>
         </is>
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
-          <t>Les Diablerets, Switzerland</t>
+          <t>Hannover, Germany</t>
         </is>
       </c>
       <c r="I108" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="J108" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="K108" s="7" t="inlineStr">
         <is>
-          <t>2027-06-13</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="L108" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="M108" s="7" t="inlineStr">
         <is>
-          <t>https://www.grc.org/quantum-sensing-conference/2027/</t>
-        </is>
-      </c>
-      <c r="N108" s="5" t="n">
-        <v>3</v>
+          <t>https://www.dpg-physik.de/veranstaltungen/2027/dpg-fruehjahrstagung-hannover</t>
+        </is>
+      </c>
+      <c r="N108" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="O108" s="7" t="inlineStr">
         <is>
-          <t>Covers photonic-platform quantum sensing (NV/atomic/solid-state), adjacent to single-photon and quantum-optics interests</t>
+          <t>DPG spring meeting for quantum optics and photonics — easily accessible from Münster</t>
         </is>
       </c>
       <c r="P108" s="7" t="inlineStr">
@@ -10764,29 +10764,29 @@
       </c>
       <c r="R108" s="7" t="inlineStr">
         <is>
-          <t>new entry</t>
+          <t>dates reconfirmed unchanged; updated to specific DPG event page (dedicated hannover-conference microsite not yet live, expected ~Sep 2026); an ambiguous/unverified cancellation signal was found in secondary search snippets — flagged for manual re-check, not acted on</t>
         </is>
       </c>
       <c r="S108" s="7" t="inlineStr">
         <is>
-          <t>https://www.grc.org/quantum-sensing-conference/2027/</t>
+          <t>https://dpg-physik.de/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>grc-qclm-2027</t>
+          <t>ofc-2027</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>Gordon Research Conference — Quantum Control of Light and Matter 2027</t>
+          <t>Optical Fiber Communication Conference 2027</t>
         </is>
       </c>
       <c r="C109" s="7" t="inlineStr">
         <is>
-          <t>GRC QCLM 2027</t>
+          <t>OFC 2027</t>
         </is>
       </c>
       <c r="D109" s="7" t="inlineStr">
@@ -10796,32 +10796,32 @@
       </c>
       <c r="E109" s="7" t="inlineStr">
         <is>
-          <t>quantum optics;nonlinear optics</t>
+          <t>photonic integrated circuits;silicon photonics;quantum communication</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>2027-08-01</t>
+          <t>2027-03-07</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>2027-08-06</t>
+          <t>2027-03-11</t>
         </is>
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
-          <t>Newport, RI, USA</t>
+          <t>Los Angeles, CA, USA</t>
         </is>
       </c>
       <c r="I109" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="J109" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="K109" s="7" t="inlineStr">
@@ -10831,12 +10831,12 @@
       </c>
       <c r="L109" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="M109" s="7" t="inlineStr">
         <is>
-          <t>https://www.grc.org/quantum-control-of-light-and-matter-conference/</t>
+          <t>https://ofcconference.org/</t>
         </is>
       </c>
       <c r="N109" s="6" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O109" s="7" t="inlineStr">
         <is>
-          <t>Directly on quantum control of light-matter interaction, nonlinear optics and ultrafast laser technology</t>
+          <t>World's largest optical comms conference with PIC and quantum networking sessions</t>
         </is>
       </c>
       <c r="P109" s="7" t="inlineStr">
@@ -10859,54 +10859,54 @@
       </c>
       <c r="R109" s="7" t="inlineStr">
         <is>
-          <t>new entry</t>
+          <t>dates/venue reconfirmed unchanged; deadlines not yet published</t>
         </is>
       </c>
       <c r="S109" s="7" t="inlineStr">
         <is>
-          <t>https://www.grc.org/quantum-control-of-light-and-matter-conference/</t>
+          <t>https://ofcconference.org/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>ieee-rapid-2027</t>
+          <t>les-houches-photonics-ai-2027</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
         <is>
-          <t>IEEE Research and Applications of Photonics in Defense 2027</t>
+          <t>Les Houches School: Photonics and Artificial Intelligence</t>
         </is>
       </c>
       <c r="C110" s="7" t="inlineStr">
         <is>
-          <t>IEEE RAPID 2027</t>
+          <t>LH Photonics-AI 2027</t>
         </is>
       </c>
       <c r="D110" s="7" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Summer School</t>
         </is>
       </c>
       <c r="E110" s="7" t="inlineStr">
         <is>
-          <t>single-photon sources;quantum communication</t>
+          <t>photonic integrated circuits;nanophotonics</t>
         </is>
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>2027-08-11</t>
+          <t>2027-04-04</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>2027-08-13</t>
+          <t>2027-04-09</t>
         </is>
       </c>
       <c r="H110" s="7" t="inlineStr">
         <is>
-          <t>Miramar Beach, FL, USA</t>
+          <t>Les Houches, France</t>
         </is>
       </c>
       <c r="I110" s="7" t="inlineStr">
@@ -10916,7 +10916,7 @@
       </c>
       <c r="J110" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K110" s="7" t="inlineStr">
@@ -10926,20 +10926,20 @@
       </c>
       <c r="L110" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="M110" s="7" t="inlineStr">
         <is>
-          <t>https://ieee-rapid.org/</t>
-        </is>
-      </c>
-      <c r="N110" s="3" t="n">
-        <v>2</v>
+          <t>https://www.houches-school-physics.com/program/program-2027/</t>
+        </is>
+      </c>
+      <c r="N110" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="O110" s="7" t="inlineStr">
         <is>
-          <t>Defense photonics conference</t>
+          <t>New 2027 Les Houches thematic school on integrated photonics and AI-assisted photonic design (organizers incl. C2N, FEMTO-ST)</t>
         </is>
       </c>
       <c r="P110" s="7" t="inlineStr">
@@ -10954,29 +10954,29 @@
       </c>
       <c r="R110" s="7" t="inlineStr">
         <is>
-          <t>could not independently reconfirm this run (search results inconclusive); kept prior data</t>
+          <t>new entry</t>
         </is>
       </c>
       <c r="S110" s="7" t="inlineStr">
         <is>
-          <t>https://ieee-rapid.org/</t>
+          <t>https://www.sfoptique.org/pages/sfo/ecoles-thematiques/2027-artificial-intelligence-photonics/2027-photonics-artificial-intelligence.html</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>ecoc-2027</t>
+          <t>spie-oo-2027</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
         <is>
-          <t>European Conference on Optical Communication 2027</t>
+          <t>SPIE Optics + Optoelectronics 2027</t>
         </is>
       </c>
       <c r="C111" s="7" t="inlineStr">
         <is>
-          <t>ECOC 2027</t>
+          <t>SPIE O+O 2027</t>
         </is>
       </c>
       <c r="D111" s="7" t="inlineStr">
@@ -10986,22 +10986,22 @@
       </c>
       <c r="E111" s="7" t="inlineStr">
         <is>
-          <t>photonic integrated circuits;silicon photonics;quantum communication;integrated quantum photonics</t>
+          <t>integrated quantum photonics;quantum optics;nanophotonics</t>
         </is>
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>2027-10-10</t>
+          <t>2027-04-05</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>2027-10-14</t>
+          <t>2027-04-08</t>
         </is>
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
-          <t>Milano, Italy</t>
+          <t>Prague, Czech Republic</t>
         </is>
       </c>
       <c r="I111" s="7" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="M111" s="7" t="inlineStr">
         <is>
-          <t>https://ecoc2027.org/</t>
+          <t>https://spie.org/conferences-and-exhibitions/optics-and-optoelectronics</t>
         </is>
       </c>
       <c r="N111" s="6" t="n">
@@ -11034,7 +11034,7 @@
       </c>
       <c r="O111" s="7" t="inlineStr">
         <is>
-          <t>Europe's flagship optical comms conference with quantum technologies track</t>
+          <t>SPIE European conference with quantum photonics and nanophotonics tracks</t>
         </is>
       </c>
       <c r="P111" s="7" t="inlineStr">
@@ -11049,29 +11049,29 @@
       </c>
       <c r="R111" s="7" t="inlineStr">
         <is>
-          <t>new entry</t>
+          <t>official website confirmed: spie.org/conferences-and-exhibitions/optics-and-optoelectronics (was unknown/TBA on file)</t>
         </is>
       </c>
       <c r="S111" s="7" t="inlineStr">
         <is>
-          <t>https://ecoc2027.org/; https://10times.com/e1hz-x284-kp7s-x-european-conference-optical-communication</t>
+          <t>original list</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>ipc-2027</t>
+          <t>quantum-networks-summit-2027</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
         <is>
-          <t>IEEE Photonics Conference 2027</t>
+          <t>Quantum Networks Summit 2027</t>
         </is>
       </c>
       <c r="C112" s="7" t="inlineStr">
         <is>
-          <t>IPC 2027</t>
+          <t>QNS 2027</t>
         </is>
       </c>
       <c r="D112" s="7" t="inlineStr">
@@ -11081,32 +11081,32 @@
       </c>
       <c r="E112" s="7" t="inlineStr">
         <is>
-          <t>integrated quantum photonics;photonic integrated circuits;silicon photonics</t>
+          <t>quantum communication;quantum networking;QKD</t>
         </is>
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>2027-11-10</t>
+          <t>2027-04-07</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>2027-11-14</t>
+          <t>2027-04-08</t>
         </is>
       </c>
       <c r="H112" s="7" t="inlineStr">
         <is>
-          <t>Eindhoven, Netherlands</t>
+          <t>Paris, France</t>
         </is>
       </c>
       <c r="I112" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J112" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K112" s="7" t="inlineStr">
@@ -11121,7 +11121,7 @@
       </c>
       <c r="M112" s="7" t="inlineStr">
         <is>
-          <t>https://ieee-ipc.org/</t>
+          <t>https://www.uppersideconferences.com/quantum-networks/2027/index.html</t>
         </is>
       </c>
       <c r="N112" s="6" t="n">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="O112" s="7" t="inlineStr">
         <is>
-          <t>IEEE photonics flagship; European edition in Eindhoven — low travel cost</t>
+          <t>Industry/research summit on quantum communications and photonic secure networking</t>
         </is>
       </c>
       <c r="P112" s="7" t="inlineStr">
@@ -11144,54 +11144,54 @@
       </c>
       <c r="R112" s="7" t="inlineStr">
         <is>
-          <t>could not independently reconfirm Eindhoven location this run (no corroborating source found); kept prior data</t>
+          <t>new entry</t>
         </is>
       </c>
       <c r="S112" s="7" t="inlineStr">
         <is>
-          <t>https://ieee-ipc.org/</t>
+          <t>https://www.uppersideconferences.com/quantum-networks/2027/index.html</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>benasque-qsi-2028</t>
+          <t>qpain-2027</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
         <is>
-          <t>Quantum Science: Implementations 2028</t>
+          <t>3rd IEEE International Conference on Quantum Photonics, AI, and Networking</t>
         </is>
       </c>
       <c r="C113" s="7" t="inlineStr">
         <is>
-          <t>Benasque QSI 2028</t>
+          <t>IEEE QPAIN 2027</t>
         </is>
       </c>
       <c r="D113" s="7" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="E113" s="7" t="inlineStr">
         <is>
-          <t>integrated quantum photonics;quantum computing hardware;quantum communication</t>
+          <t>integrated quantum photonics;quantum networking</t>
         </is>
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-04-08</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-04-10</t>
         </is>
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
-          <t>Benasque, Spain</t>
+          <t>Chattogram, Bangladesh</t>
         </is>
       </c>
       <c r="I113" s="7" t="inlineStr">
@@ -11201,7 +11201,7 @@
       </c>
       <c r="J113" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="K113" s="7" t="inlineStr">
@@ -11211,20 +11211,20 @@
       </c>
       <c r="L113" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="M113" s="7" t="inlineStr">
         <is>
-          <t>https://benasque.org/</t>
-        </is>
-      </c>
-      <c r="N113" s="6" t="n">
-        <v>4</v>
+          <t>https://qpain.org/</t>
+        </is>
+      </c>
+      <c r="N113" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="O113" s="7" t="inlineStr">
         <is>
-          <t>Benasque workshop on quantum implementations including photonic platforms</t>
+          <t>Successor of the already-archived IEEE QPAIN 2026; regional IEEE conference on quantum photonics/networking</t>
         </is>
       </c>
       <c r="P113" s="7" t="inlineStr">
@@ -11239,29 +11239,29 @@
       </c>
       <c r="R113" s="7" t="inlineStr">
         <is>
-          <t>new entry; year roll-over; biennial series, 2028 not yet announced</t>
+          <t>new entry</t>
         </is>
       </c>
       <c r="S113" s="7" t="inlineStr">
         <is>
-          <t>https://benasque.org/</t>
+          <t>https://qpain.org/</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>damop-2027</t>
+          <t>aps-summit-2027</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>58th APS Division of Atomic, Molecular and Optical Physics Meeting</t>
+          <t>APS Global Physics Summit 2027</t>
         </is>
       </c>
       <c r="C114" s="7" t="inlineStr">
         <is>
-          <t>DAMOP 2027</t>
+          <t>APS Summit 2027</t>
         </is>
       </c>
       <c r="D114" s="7" t="inlineStr">
@@ -11271,22 +11271,22 @@
       </c>
       <c r="E114" s="7" t="inlineStr">
         <is>
-          <t>quantum optics;nonlinear optics;single-photon sources</t>
+          <t>quantum optics;quantum computing hardware;integrated quantum photonics</t>
         </is>
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-04-11</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-04-16</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
-          <t>Chicago, IL, USA</t>
+          <t>Atlanta, GA, USA</t>
         </is>
       </c>
       <c r="I114" s="7" t="inlineStr">
@@ -11311,15 +11311,15 @@
       </c>
       <c r="M114" s="7" t="inlineStr">
         <is>
-          <t>https://www.aps.org/events/2027/damop-2027</t>
-        </is>
-      </c>
-      <c r="N114" s="5" t="n">
-        <v>3</v>
+          <t>https://www.aps.org/events/2027/summit</t>
+        </is>
+      </c>
+      <c r="N114" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="O114" s="7" t="inlineStr">
         <is>
-          <t>AMO physics flagship with quantum optics and single-photon sessions</t>
+          <t>Joint APS March+April meeting; major quantum photonics and computing sessions</t>
         </is>
       </c>
       <c r="P114" s="7" t="inlineStr">
@@ -11334,29 +11334,29 @@
       </c>
       <c r="R114" s="7" t="inlineStr">
         <is>
-          <t>new entry; year roll-over; Chicago confirmed, exact June dates not yet published</t>
+          <t>dates/venue reconfirmed unchanged; deadlines not yet published</t>
         </is>
       </c>
       <c r="S114" s="7" t="inlineStr">
         <is>
-          <t>https://www.aps.org/events/2027/damop-2027</t>
+          <t>https://www.aps.org/events/2027/summit</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>ecio-2027</t>
+          <t>pic-international-2027</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
         <is>
-          <t>European Conference on Integrated Optics 2027</t>
+          <t>PIC International 2027</t>
         </is>
       </c>
       <c r="C115" s="7" t="inlineStr">
         <is>
-          <t>ECIO 2027</t>
+          <t>PIC International</t>
         </is>
       </c>
       <c r="D115" s="7" t="inlineStr">
@@ -11366,32 +11366,32 @@
       </c>
       <c r="E115" s="7" t="inlineStr">
         <is>
-          <t>integrated quantum photonics;photonic integrated circuits;silicon photonics;nanophotonics</t>
+          <t>photonic integrated circuits;silicon photonics</t>
         </is>
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-04-12</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-04-14</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Brussels, Belgium</t>
         </is>
       </c>
       <c r="I115" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J115" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K115" s="7" t="inlineStr">
@@ -11406,15 +11406,15 @@
       </c>
       <c r="M115" s="7" t="inlineStr">
         <is>
-          <t>https://ecio-conference.org/</t>
-        </is>
-      </c>
-      <c r="N115" s="4" t="n">
-        <v>5</v>
+          <t>https://picinternational.net/</t>
+        </is>
+      </c>
+      <c r="N115" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="O115" s="7" t="inlineStr">
         <is>
-          <t>Largest European integrated optics conference — core relevance for AG Schuck</t>
+          <t>12th edition of the PIC industry conference; useful for PIC industry contacts</t>
         </is>
       </c>
       <c r="P115" s="7" t="inlineStr">
@@ -11429,29 +11429,29 @@
       </c>
       <c r="R115" s="7" t="inlineStr">
         <is>
-          <t>new entry; year roll-over; annual series, 2027 host not yet announced</t>
+          <t>new entry</t>
         </is>
       </c>
       <c r="S115" s="7" t="inlineStr">
         <is>
-          <t>https://ecio-conference.org/</t>
+          <t>https://picinternational.net/; https://10times.com/pic-international-conference</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>egas-2027</t>
+          <t>cleo-2027</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>58th Conference of the European Group on Atomic Systems</t>
+          <t>Conference on Lasers and Electro-Optics 2027</t>
         </is>
       </c>
       <c r="C116" s="7" t="inlineStr">
         <is>
-          <t>EGAS 2027</t>
+          <t>CLEO 2027</t>
         </is>
       </c>
       <c r="D116" s="7" t="inlineStr">
@@ -11461,22 +11461,22 @@
       </c>
       <c r="E116" s="7" t="inlineStr">
         <is>
-          <t>quantum optics;nonlinear optics</t>
+          <t>integrated quantum photonics;quantum optics;nonlinear optics;silicon photonics;single-photon sources</t>
         </is>
       </c>
       <c r="F116" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-05-02</t>
         </is>
       </c>
       <c r="G116" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-05-06</t>
         </is>
       </c>
       <c r="H116" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Long Beach, CA, USA</t>
         </is>
       </c>
       <c r="I116" s="7" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="J116" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K116" s="7" t="inlineStr">
@@ -11501,15 +11501,15 @@
       </c>
       <c r="M116" s="7" t="inlineStr">
         <is>
-          <t>https://www.eps-egas.org/</t>
-        </is>
-      </c>
-      <c r="N116" s="5" t="n">
-        <v>3</v>
+          <t>https://cleoconference.org/</t>
+        </is>
+      </c>
+      <c r="N116" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="O116" s="7" t="inlineStr">
         <is>
-          <t>European atomic systems conference with quantum optics and light-matter sessions</t>
+          <t>Premier US laser/photonics conference; major IQP, Si-PIC and quantum optics sessions</t>
         </is>
       </c>
       <c r="P116" s="7" t="inlineStr">
@@ -11524,54 +11524,54 @@
       </c>
       <c r="R116" s="7" t="inlineStr">
         <is>
-          <t>new entry; year roll-over; annual series, host not yet announced (unverified rumor of Sweden discarded)</t>
+          <t>new entry; year roll-over from 2026 edition (Charlotte)</t>
         </is>
       </c>
       <c r="S116" s="7" t="inlineStr">
         <is>
-          <t>https://www.eps-egas.org/</t>
+          <t>https://cleoconference.org/; https://www.optica.org/events/global_calendar/events/2027/conference_on_lasers_and_electro-optics_(1)/</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>erice-matter-photonics-2026</t>
+          <t>ccw-amsterdam-2027</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>40th Erice Workshop: Matter Physics and Photonics</t>
+          <t>Critical Communications World Amsterdam 2027</t>
         </is>
       </c>
       <c r="C117" s="7" t="inlineStr">
         <is>
-          <t>Erice MPP 2026</t>
+          <t>CCW 2027</t>
         </is>
       </c>
       <c r="D117" s="7" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="E117" s="7" t="inlineStr">
         <is>
-          <t>nanophotonics;quantum optics</t>
+          <t>quantum communication;quantum networking</t>
         </is>
       </c>
       <c r="F117" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-05-11</t>
         </is>
       </c>
       <c r="G117" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-05-13</t>
         </is>
       </c>
       <c r="H117" s="7" t="inlineStr">
         <is>
-          <t>Erice, Italy</t>
+          <t>Amsterdam, Netherlands</t>
         </is>
       </c>
       <c r="I117" s="7" t="inlineStr">
@@ -11581,7 +11581,7 @@
       </c>
       <c r="J117" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="K117" s="7" t="inlineStr">
@@ -11591,20 +11591,20 @@
       </c>
       <c r="L117" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="M117" s="7" t="inlineStr">
         <is>
-          <t>https://ettoremajoranafoundation.com/</t>
-        </is>
-      </c>
-      <c r="N117" s="6" t="n">
-        <v>4</v>
+          <t>https://www.critical-communications-world.com/</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="O117" s="7" t="inlineStr">
         <is>
-          <t>Erice workshop (director M. Cesaria) centered on photonics and its interplay with matter physics</t>
+          <t>Critical comms industry event; QKD sessions of marginal relevance</t>
         </is>
       </c>
       <c r="P117" s="7" t="inlineStr">
@@ -11619,29 +11619,29 @@
       </c>
       <c r="R117" s="7" t="inlineStr">
         <is>
-          <t>new entry; exact 2026 dates not yet published</t>
+          <t>new entry; year roll-over; confirmed via organizer's exhibitor page</t>
         </is>
       </c>
       <c r="S117" s="7" t="inlineStr">
         <is>
-          <t>https://ettoremajoranafoundation.com/wp-content/uploads/2026/03/Summary-2026-1-1.pdf</t>
+          <t>https://www.critical-communications-world.com/exhibit-at-ccw</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>grc-comp-optics-photonics-2027</t>
+          <t>quantum-tech-world-2027</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>Gordon Research Conference — Computational Optics and Intelligent Photonic Devices 2027</t>
+          <t>Quantum.Tech World 2027</t>
         </is>
       </c>
       <c r="C118" s="7" t="inlineStr">
         <is>
-          <t>GRC COIPD 2027</t>
+          <t>Q.Tech World 2027</t>
         </is>
       </c>
       <c r="D118" s="7" t="inlineStr">
@@ -11651,55 +11651,55 @@
       </c>
       <c r="E118" s="7" t="inlineStr">
         <is>
-          <t>integrated quantum photonics;photonic integrated circuits;nanophotonics</t>
+          <t>quantum computing hardware;quantum communication;integrated quantum photonics</t>
         </is>
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-05-25</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-05-26</t>
         </is>
       </c>
       <c r="H118" s="7" t="inlineStr">
         <is>
-          <t>Manchester, NH, USA</t>
+          <t>Boston, MA, USA</t>
         </is>
       </c>
       <c r="I118" s="7" t="inlineStr">
         <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="J118" s="7" t="inlineStr">
+        <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="J118" s="7" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
       <c r="K118" s="7" t="inlineStr">
         <is>
-          <t>2027-06-27</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="L118" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="M118" s="7" t="inlineStr">
         <is>
-          <t>https://www.grc.org/computational-optics-and-intelligent-photonic-devices-conference/2027/</t>
-        </is>
-      </c>
-      <c r="N118" s="5" t="n">
-        <v>3</v>
+          <t>https://www.alphaevents.com/events-quantumtechus</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="O118" s="7" t="inlineStr">
         <is>
-          <t>New GRC series on integrated photonic platforms, metasurfaces and photonic inverse design</t>
+          <t>Industry quantum technology event; limited deep-science content</t>
         </is>
       </c>
       <c r="P118" s="7" t="inlineStr">
@@ -11714,29 +11714,29 @@
       </c>
       <c r="R118" s="7" t="inlineStr">
         <is>
-          <t>new entry; inaugural/new series, exact dates not yet posted</t>
+          <t>new entry; year roll-over; 8th edition, Encore Boston Harbor, first year co-located with Compute.Tech</t>
         </is>
       </c>
       <c r="S118" s="7" t="inlineStr">
         <is>
-          <t>https://www.grc.org/computational-optics-and-intelligent-photonic-devices-conference/2027/</t>
+          <t>https://www.alphaevents.com/events-quantumtechus</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>grc-quantum-science-2028</t>
+          <t>cleo-europe-2027</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>Gordon Research Conference — Quantum Science 2028</t>
+          <t>CLEO/Europe-EQEC 2027</t>
         </is>
       </c>
       <c r="C119" s="7" t="inlineStr">
         <is>
-          <t>GRC QS 2028</t>
+          <t>CLEO/Europe 2027</t>
         </is>
       </c>
       <c r="D119" s="7" t="inlineStr">
@@ -11746,22 +11746,22 @@
       </c>
       <c r="E119" s="7" t="inlineStr">
         <is>
-          <t>quantum optics;quantum computing hardware;quantum communication;integrated quantum photonics</t>
+          <t>integrated quantum photonics;quantum optics;nonlinear optics;nanophotonics</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-06-20</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-06-25</t>
         </is>
       </c>
       <c r="H119" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Munich, Germany</t>
         </is>
       </c>
       <c r="I119" s="7" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="J119" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="K119" s="7" t="inlineStr">
@@ -11781,20 +11781,20 @@
       </c>
       <c r="L119" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="M119" s="7" t="inlineStr">
         <is>
-          <t>https://www.grc.org/quantum-science-conference/</t>
-        </is>
-      </c>
-      <c r="N119" s="6" t="n">
-        <v>4</v>
+          <t>https://cleoeurope.org/</t>
+        </is>
+      </c>
+      <c r="N119" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="O119" s="7" t="inlineStr">
         <is>
-          <t>GRC on quantum science covering photonic quantum systems and quantum information</t>
+          <t>Flagship European photonics and quantum optics biennial conference</t>
         </is>
       </c>
       <c r="P119" s="7" t="inlineStr">
@@ -11809,29 +11809,29 @@
       </c>
       <c r="R119" s="7" t="inlineStr">
         <is>
-          <t>new entry; year roll-over; biennial series, 2028 dates not yet published</t>
+          <t>dates/venue reconfirmed unchanged via World of Photonics Congress page; abstract deadline not yet announced (2025 cycle's was late Jan)</t>
         </is>
       </c>
       <c r="S119" s="7" t="inlineStr">
         <is>
-          <t>https://www.grc.org/quantum-science-conference/</t>
+          <t>https://cleoeurope.org/; https://www.photonics-congress.com/en/about/conferences/cleo-eqec/</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>icap-2029</t>
+          <t>grc-quantum-sensing-2027</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>30th International Conference on Atomic Physics</t>
+          <t>Gordon Research Conference — Quantum Sensing 2027</t>
         </is>
       </c>
       <c r="C120" s="7" t="inlineStr">
         <is>
-          <t>ICAP 2029</t>
+          <t>GRC QSe 2027</t>
         </is>
       </c>
       <c r="D120" s="7" t="inlineStr">
@@ -11841,47 +11841,47 @@
       </c>
       <c r="E120" s="7" t="inlineStr">
         <is>
-          <t>quantum optics;nonlinear optics</t>
+          <t>quantum optics;single-photon sources;quantum computing hardware</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-07-11</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-07-16</t>
         </is>
       </c>
       <c r="H120" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Les Diablerets, Switzerland</t>
         </is>
       </c>
       <c r="I120" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J120" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K120" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-06-13</t>
         </is>
       </c>
       <c r="L120" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="M120" s="7" t="inlineStr">
         <is>
-          <t>https://www.icap29.com/</t>
+          <t>https://www.grc.org/quantum-sensing-conference/2027/</t>
         </is>
       </c>
       <c r="N120" s="5" t="n">
@@ -11889,7 +11889,7 @@
       </c>
       <c r="O120" s="7" t="inlineStr">
         <is>
-          <t>Atomic physics conference with quantum optics and light-matter interaction sessions</t>
+          <t>Covers photonic-platform quantum sensing (NV/atomic/solid-state), adjacent to single-photon and quantum-optics interests</t>
         </is>
       </c>
       <c r="P120" s="7" t="inlineStr">
@@ -11904,29 +11904,29 @@
       </c>
       <c r="R120" s="7" t="inlineStr">
         <is>
-          <t>new entry; year roll-over; triennial series, host not yet announced</t>
+          <t>new entry</t>
         </is>
       </c>
       <c r="S120" s="7" t="inlineStr">
         <is>
-          <t>https://www.icap29.com/</t>
+          <t>https://www.grc.org/quantum-sensing-conference/2027/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>iqt-nordics-2027</t>
+          <t>grc-qclm-2027</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>IQT Nordics 2027</t>
+          <t>Gordon Research Conference — Quantum Control of Light and Matter 2027</t>
         </is>
       </c>
       <c r="C121" s="7" t="inlineStr">
         <is>
-          <t>IQT Nordics 2027</t>
+          <t>GRC QCLM 2027</t>
         </is>
       </c>
       <c r="D121" s="7" t="inlineStr">
@@ -11936,27 +11936,27 @@
       </c>
       <c r="E121" s="7" t="inlineStr">
         <is>
-          <t>quantum communication;quantum computing hardware;integrated quantum photonics</t>
+          <t>quantum optics;nonlinear optics</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-08-01</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-08-06</t>
         </is>
       </c>
       <c r="H121" s="7" t="inlineStr">
         <is>
-          <t>Copenhagen, Denmark</t>
+          <t>Newport, RI, USA</t>
         </is>
       </c>
       <c r="I121" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J121" s="7" t="inlineStr">
@@ -11971,20 +11971,20 @@
       </c>
       <c r="L121" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="M121" s="7" t="inlineStr">
         <is>
-          <t>https://iqtevent.com/nordics/</t>
-        </is>
-      </c>
-      <c r="N121" s="5" t="n">
-        <v>3</v>
+          <t>https://www.grc.org/quantum-control-of-light-and-matter-conference/</t>
+        </is>
+      </c>
+      <c r="N121" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="O121" s="7" t="inlineStr">
         <is>
-          <t>Nordic quantum industry conference with hardware and QKD sessions</t>
+          <t>Directly on quantum control of light-matter interaction, nonlinear optics and ultrafast laser technology</t>
         </is>
       </c>
       <c r="P121" s="7" t="inlineStr">
@@ -11999,29 +11999,29 @@
       </c>
       <c r="R121" s="7" t="inlineStr">
         <is>
-          <t>new entry; year roll-over; organizer confirmed Copenhagen return (rotation Copenhagen/Helsinki/Gothenburg/Oslo), exact dates TBA</t>
+          <t>new entry</t>
         </is>
       </c>
       <c r="S121" s="7" t="inlineStr">
         <is>
-          <t>https://iqtevent.com/nordics/; https://www.insidequantumtechnology.com/news-archive/announcing-the-return-of-iqt-nordics-in-copenhagen-2027/</t>
+          <t>https://www.grc.org/quantum-control-of-light-and-matter-conference/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>islc-2028</t>
+          <t>ieee-rapid-2027</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>31st International Semiconductor Laser Conference</t>
+          <t>IEEE Research and Applications of Photonics in Defense 2027</t>
         </is>
       </c>
       <c r="C122" s="7" t="inlineStr">
         <is>
-          <t>ISLC 2028</t>
+          <t>IEEE RAPID 2027</t>
         </is>
       </c>
       <c r="D122" s="7" t="inlineStr">
@@ -12031,22 +12031,22 @@
       </c>
       <c r="E122" s="7" t="inlineStr">
         <is>
-          <t>single-photon sources;III-V on Si;photonic integrated circuits</t>
+          <t>single-photon sources;quantum communication</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-08-11</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-08-13</t>
         </is>
       </c>
       <c r="H122" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Miramar Beach, FL, USA</t>
         </is>
       </c>
       <c r="I122" s="7" t="inlineStr">
@@ -12071,15 +12071,15 @@
       </c>
       <c r="M122" s="7" t="inlineStr">
         <is>
-          <t>https://ieeephotonics.org/conferences/</t>
-        </is>
-      </c>
-      <c r="N122" s="6" t="n">
-        <v>4</v>
+          <t>https://ieee-rapid.org/</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="O122" s="7" t="inlineStr">
         <is>
-          <t>III-V semiconductor laser conference — key for quantum light source development</t>
+          <t>Defense photonics conference</t>
         </is>
       </c>
       <c r="P122" s="7" t="inlineStr">
@@ -12094,29 +12094,29 @@
       </c>
       <c r="R122" s="7" t="inlineStr">
         <is>
-          <t>new entry; year roll-over; biennial series, host not yet announced</t>
+          <t>could not independently reconfirm this run (search results inconclusive); kept prior data</t>
         </is>
       </c>
       <c r="S122" s="7" t="inlineStr">
         <is>
-          <t>https://ieeephotonics.org/conferences/</t>
+          <t>https://ieee-rapid.org/</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>nrw-nano-2027</t>
+          <t>ecoc-2027</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>12th NRW Nano Conference</t>
+          <t>European Conference on Optical Communication 2027</t>
         </is>
       </c>
       <c r="C123" s="7" t="inlineStr">
         <is>
-          <t>NRW Nano 2027</t>
+          <t>ECOC 2027</t>
         </is>
       </c>
       <c r="D123" s="7" t="inlineStr">
@@ -12126,22 +12126,22 @@
       </c>
       <c r="E123" s="7" t="inlineStr">
         <is>
-          <t>nanophotonics;photonic integrated circuits</t>
+          <t>photonic integrated circuits;silicon photonics;quantum communication;integrated quantum photonics</t>
         </is>
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-10-10</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-10-14</t>
         </is>
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
-          <t>North Rhine-Westphalia, Germany</t>
+          <t>Milano, Italy</t>
         </is>
       </c>
       <c r="I123" s="7" t="inlineStr">
@@ -12166,15 +12166,15 @@
       </c>
       <c r="M123" s="7" t="inlineStr">
         <is>
-          <t>https://www.nanoconference.de/</t>
-        </is>
-      </c>
-      <c r="N123" s="5" t="n">
-        <v>3</v>
+          <t>https://ecoc2027.org/</t>
+        </is>
+      </c>
+      <c r="N123" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="O123" s="7" t="inlineStr">
         <is>
-          <t>Regional NRW nanotechnology conference; local access</t>
+          <t>Europe's flagship optical comms conference with quantum technologies track</t>
         </is>
       </c>
       <c r="P123" s="7" t="inlineStr">
@@ -12189,29 +12189,29 @@
       </c>
       <c r="R123" s="7" t="inlineStr">
         <is>
-          <t>renamed from 'nrw-nano-2026' placeholder; confirmed biennial series (11th ed. was Sep 30-Oct 1 2025, Dortmund), 2026 edition does not exist, next expected 2027 dates TBA</t>
+          <t>new entry</t>
         </is>
       </c>
       <c r="S123" s="7" t="inlineStr">
         <is>
-          <t>original list</t>
+          <t>https://ecoc2027.org/; https://10times.com/e1hz-x284-kp7s-x-european-conference-optical-communication</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>oecc-2027</t>
+          <t>ipc-2027</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>32nd OptoElectronics and Communications Conference</t>
+          <t>IEEE Photonics Conference 2027</t>
         </is>
       </c>
       <c r="C124" s="7" t="inlineStr">
         <is>
-          <t>OECC 2027</t>
+          <t>IPC 2027</t>
         </is>
       </c>
       <c r="D124" s="7" t="inlineStr">
@@ -12221,22 +12221,22 @@
       </c>
       <c r="E124" s="7" t="inlineStr">
         <is>
-          <t>photonic integrated circuits;silicon photonics;quantum communication</t>
+          <t>integrated quantum photonics;photonic integrated circuits;silicon photonics</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-11-10</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>2027-11-14</t>
         </is>
       </c>
       <c r="H124" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Eindhoven, Netherlands</t>
         </is>
       </c>
       <c r="I124" s="7" t="inlineStr">
@@ -12261,15 +12261,15 @@
       </c>
       <c r="M124" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="N124" s="5" t="n">
-        <v>3</v>
+          <t>https://ieee-ipc.org/</t>
+        </is>
+      </c>
+      <c r="N124" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="O124" s="7" t="inlineStr">
         <is>
-          <t>Asia-Pacific optoelectronics and comms conference with PIC sessions</t>
+          <t>IEEE photonics flagship; European edition in Eindhoven — low travel cost</t>
         </is>
       </c>
       <c r="P124" s="7" t="inlineStr">
@@ -12284,39 +12284,39 @@
       </c>
       <c r="R124" s="7" t="inlineStr">
         <is>
-          <t>new entry; year roll-over; annual, rotating Asia-Pacific host, 2027 not yet announced</t>
+          <t>could not independently reconfirm Eindhoven location this run (no corroborating source found); kept prior data</t>
         </is>
       </c>
       <c r="S124" s="7" t="inlineStr">
         <is>
-          <t>original list</t>
+          <t>https://ieee-ipc.org/</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>opic-2027</t>
+          <t>benasque-qsi-2028</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>OPIC 2027 — Optics &amp; Photonics International Congress</t>
+          <t>Quantum Science: Implementations 2028</t>
         </is>
       </c>
       <c r="C125" s="7" t="inlineStr">
         <is>
-          <t>OPIC 2027</t>
+          <t>Benasque QSI 2028</t>
         </is>
       </c>
       <c r="D125" s="7" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="E125" s="7" t="inlineStr">
         <is>
-          <t>integrated quantum photonics;quantum optics;nanophotonics</t>
+          <t>integrated quantum photonics;quantum computing hardware;quantum communication</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="H125" s="7" t="inlineStr">
         <is>
-          <t>Yokohama, Japan (expected)</t>
+          <t>Benasque, Spain</t>
         </is>
       </c>
       <c r="I125" s="7" t="inlineStr">
@@ -12341,7 +12341,7 @@
       </c>
       <c r="J125" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="K125" s="7" t="inlineStr">
@@ -12351,20 +12351,20 @@
       </c>
       <c r="L125" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="M125" s="7" t="inlineStr">
         <is>
-          <t>https://opicon.jp/</t>
-        </is>
-      </c>
-      <c r="N125" s="5" t="n">
-        <v>3</v>
+          <t>https://benasque.org/</t>
+        </is>
+      </c>
+      <c r="N125" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="O125" s="7" t="inlineStr">
         <is>
-          <t>Japanese international photonics congress with quantum tracks</t>
+          <t>Benasque workshop on quantum implementations including photonic platforms</t>
         </is>
       </c>
       <c r="P125" s="7" t="inlineStr">
@@ -12379,29 +12379,29 @@
       </c>
       <c r="R125" s="7" t="inlineStr">
         <is>
-          <t>new entry; annual series (every April, Pacifico Yokohama), 2027 dates not yet announced</t>
+          <t>new entry; year roll-over; biennial series, 2028 not yet announced</t>
         </is>
       </c>
       <c r="S125" s="7" t="inlineStr">
         <is>
-          <t>https://opicon.jp/</t>
+          <t>https://benasque.org/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>optica-quantum-2028</t>
+          <t>damop-2027</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>Optica Quantum 2.0 Conference and Exhibition 2028</t>
+          <t>58th APS Division of Atomic, Molecular and Optical Physics Meeting</t>
         </is>
       </c>
       <c r="C126" s="7" t="inlineStr">
         <is>
-          <t>Optica Quantum 2028</t>
+          <t>DAMOP 2027</t>
         </is>
       </c>
       <c r="D126" s="7" t="inlineStr">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="E126" s="7" t="inlineStr">
         <is>
-          <t>integrated quantum photonics;quantum optics;single-photon sources;quantum communication;quantum computing hardware</t>
+          <t>quantum optics;nonlinear optics;single-photon sources</t>
         </is>
       </c>
       <c r="F126" s="7" t="inlineStr">
@@ -12426,7 +12426,7 @@
       </c>
       <c r="H126" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>Chicago, IL, USA</t>
         </is>
       </c>
       <c r="I126" s="7" t="inlineStr">
@@ -12436,7 +12436,7 @@
       </c>
       <c r="J126" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="K126" s="7" t="inlineStr">
@@ -12446,20 +12446,20 @@
       </c>
       <c r="L126" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="M126" s="7" t="inlineStr">
         <is>
-          <t>https://www.optica.org/events/topical_meetings/quantum/</t>
-        </is>
-      </c>
-      <c r="N126" s="4" t="n">
-        <v>5</v>
+          <t>https://www.aps.org/events/2027/damop-2027</t>
+        </is>
+      </c>
+      <c r="N126" s="5" t="n">
+        <v>3</v>
       </c>
       <c r="O126" s="7" t="inlineStr">
         <is>
-          <t>Premier quantum photonics conference spanning PICs, detectors, QKD, and hardware</t>
+          <t>AMO physics flagship with quantum optics and single-photon sessions</t>
         </is>
       </c>
       <c r="P126" s="7" t="inlineStr">
@@ -12474,39 +12474,39 @@
       </c>
       <c r="R126" s="7" t="inlineStr">
         <is>
-          <t>new entry; year roll-over; biennial series, 2028 not yet announced</t>
+          <t>new entry; year roll-over; Chicago confirmed, exact June dates not yet published</t>
         </is>
       </c>
       <c r="S126" s="7" t="inlineStr">
         <is>
-          <t>https://www.optica.org/events/topical_meetings/quantum/</t>
+          <t>https://www.aps.org/events/2027/damop-2027</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>owtnm-2027</t>
+          <t>ecio-2027</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>OWTNM 2027 — Optical Wave &amp; Waveguide Theory and Modelling Workshop</t>
+          <t>European Conference on Integrated Optics 2027</t>
         </is>
       </c>
       <c r="C127" s="7" t="inlineStr">
         <is>
-          <t>OWTNM 2027</t>
+          <t>ECIO 2027</t>
         </is>
       </c>
       <c r="D127" s="7" t="inlineStr">
         <is>
-          <t>Workshop</t>
+          <t>Conference</t>
         </is>
       </c>
       <c r="E127" s="7" t="inlineStr">
         <is>
-          <t>photonic integrated circuits;nanophotonics</t>
+          <t>integrated quantum photonics;photonic integrated circuits;silicon photonics;nanophotonics</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="J127" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="K127" s="7" t="inlineStr">
@@ -12541,20 +12541,20 @@
       </c>
       <c r="L127" s="7" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>TBA</t>
         </is>
       </c>
       <c r="M127" s="7" t="inlineStr">
         <is>
-          <t>https://www.owtnm.eu/</t>
-        </is>
-      </c>
-      <c r="N127" s="5" t="n">
-        <v>3</v>
+          <t>https://ecio-conference.org/</t>
+        </is>
+      </c>
+      <c r="N127" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="O127" s="7" t="inlineStr">
         <is>
-          <t>Waveguide modelling workshop relevant to PIC simulation</t>
+          <t>Largest European integrated optics conference — core relevance for AG Schuck</t>
         </is>
       </c>
       <c r="P127" s="7" t="inlineStr">
@@ -12569,29 +12569,29 @@
       </c>
       <c r="R127" s="7" t="inlineStr">
         <is>
-          <t>new entry; annual series since 1992, 2027 host not yet announced</t>
+          <t>new entry; year roll-over; annual series, 2027 host not yet announced</t>
         </is>
       </c>
       <c r="S127" s="7" t="inlineStr">
         <is>
-          <t>https://www.owtnm.eu/</t>
+          <t>https://ecio-conference.org/</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>photonics-north-2027</t>
+          <t>egas-2027</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>Photonics North 2027</t>
+          <t>58th Conference of the European Group on Atomic Systems</t>
         </is>
       </c>
       <c r="C128" s="7" t="inlineStr">
         <is>
-          <t>PN 2027</t>
+          <t>EGAS 2027</t>
         </is>
       </c>
       <c r="D128" s="7" t="inlineStr">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="E128" s="7" t="inlineStr">
         <is>
-          <t>silicon photonics;integrated quantum photonics;quantum communication</t>
+          <t>quantum optics;nonlinear optics</t>
         </is>
       </c>
       <c r="F128" s="7" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="M128" s="7" t="inlineStr">
         <is>
-          <t>https://photonicsnorth.com/en</t>
+          <t>https://www.eps-egas.org/</t>
         </is>
       </c>
       <c r="N128" s="5" t="n">
@@ -12649,7 +12649,7 @@
       </c>
       <c r="O128" s="7" t="inlineStr">
         <is>
-          <t>Canadian national photonics conference with PIC and quantum sessions</t>
+          <t>European atomic systems conference with quantum optics and light-matter sessions</t>
         </is>
       </c>
       <c r="P128" s="7" t="inlineStr">
@@ -12664,39 +12664,39 @@
       </c>
       <c r="R128" s="7" t="inlineStr">
         <is>
-          <t>new entry; year roll-over; cadence confirmed annual (2024 Vancouver, 2025 Ottawa, 2026 Québec City); 2027 not yet announced</t>
+          <t>new entry; year roll-over; annual series, host not yet announced (unverified rumor of Sweden discarded)</t>
         </is>
       </c>
       <c r="S128" s="7" t="inlineStr">
         <is>
-          <t>https://photonicsnorth.com/en</t>
+          <t>https://www.eps-egas.org/</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>quantum-korea-2027</t>
+          <t>erice-matter-photonics-2026</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>Quantum Korea 2027</t>
+          <t>40th Erice Workshop: Matter Physics and Photonics</t>
         </is>
       </c>
       <c r="C129" s="7" t="inlineStr">
         <is>
-          <t>Quantum Korea 2027</t>
+          <t>Erice MPP 2026</t>
         </is>
       </c>
       <c r="D129" s="7" t="inlineStr">
         <is>
-          <t>Conference</t>
+          <t>Workshop</t>
         </is>
       </c>
       <c r="E129" s="7" t="inlineStr">
         <is>
-          <t>quantum computing hardware;quantum communication;integrated quantum photonics</t>
+          <t>nanophotonics;quantum optics</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
@@ -12711,7 +12711,7 @@
       </c>
       <c r="H129" s="7" t="inlineStr">
         <is>
-          <t>Seoul, South Korea (expected)</t>
+          <t>Erice, Italy</t>
         </is>
       </c>
       <c r="I129" s="7" t="inlineStr">
@@ -12731,20 +12731,20 @@
       </c>
       <c r="L129" s="7" t="inlineStr">
         <is>
-          <t>TBA</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="M129" s="7" t="inlineStr">
         <is>
-          <t>https://quantum-korea.kr/en/main</t>
-        </is>
-      </c>
-      <c r="N129" s="3" t="n">
-        <v>2</v>
+          <t>https://ettoremajoranafoundation.com/</t>
+        </is>
+      </c>
+      <c r="N129" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="O129" s="7" t="inlineStr">
         <is>
-          <t>Government-organised Korean quantum technology showcase</t>
+          <t>Erice workshop (director M. Cesaria) centered on photonics and its interplay with matter physics</t>
         </is>
       </c>
       <c r="P129" s="7" t="inlineStr">
@@ -12759,105 +12759,1245 @@
       </c>
       <c r="R129" s="7" t="inlineStr">
         <is>
-          <t>new entry; year roll-over; annual series since 2023, 2027 not yet announced</t>
+          <t>new entry; exact 2026 dates not yet published</t>
         </is>
       </c>
       <c r="S129" s="7" t="inlineStr">
         <is>
-          <t>https://quantum-korea.kr/en/main</t>
+          <t>https://ettoremajoranafoundation.com/wp-content/uploads/2026/03/Summary-2026-1-1.pdf</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="7" t="inlineStr">
         <is>
+          <t>grc-comp-optics-photonics-2027</t>
+        </is>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>Gordon Research Conference — Computational Optics and Intelligent Photonic Devices 2027</t>
+        </is>
+      </c>
+      <c r="C130" s="7" t="inlineStr">
+        <is>
+          <t>GRC COIPD 2027</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>integrated quantum photonics;photonic integrated circuits;nanophotonics</t>
+        </is>
+      </c>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="H130" s="7" t="inlineStr">
+        <is>
+          <t>Manchester, NH, USA</t>
+        </is>
+      </c>
+      <c r="I130" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J130" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K130" s="7" t="inlineStr">
+        <is>
+          <t>2027-06-27</t>
+        </is>
+      </c>
+      <c r="L130" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="M130" s="7" t="inlineStr">
+        <is>
+          <t>https://www.grc.org/computational-optics-and-intelligent-photonic-devices-conference/2027/</t>
+        </is>
+      </c>
+      <c r="N130" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O130" s="7" t="inlineStr">
+        <is>
+          <t>New GRC series on integrated photonic platforms, metasurfaces and photonic inverse design</t>
+        </is>
+      </c>
+      <c r="P130" s="7" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="Q130" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="R130" s="7" t="inlineStr">
+        <is>
+          <t>new entry; inaugural/new series, exact dates not yet posted</t>
+        </is>
+      </c>
+      <c r="S130" s="7" t="inlineStr">
+        <is>
+          <t>https://www.grc.org/computational-optics-and-intelligent-photonic-devices-conference/2027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="7" t="inlineStr">
+        <is>
+          <t>grc-quantum-science-2028</t>
+        </is>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>Gordon Research Conference — Quantum Science 2028</t>
+        </is>
+      </c>
+      <c r="C131" s="7" t="inlineStr">
+        <is>
+          <t>GRC QS 2028</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>quantum optics;quantum computing hardware;quantum communication;integrated quantum photonics</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="H131" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="I131" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="J131" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K131" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="L131" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="M131" s="7" t="inlineStr">
+        <is>
+          <t>https://www.grc.org/quantum-science-conference/</t>
+        </is>
+      </c>
+      <c r="N131" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O131" s="7" t="inlineStr">
+        <is>
+          <t>GRC on quantum science covering photonic quantum systems and quantum information</t>
+        </is>
+      </c>
+      <c r="P131" s="7" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="Q131" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="R131" s="7" t="inlineStr">
+        <is>
+          <t>new entry; year roll-over; biennial series, 2028 dates not yet published</t>
+        </is>
+      </c>
+      <c r="S131" s="7" t="inlineStr">
+        <is>
+          <t>https://www.grc.org/quantum-science-conference/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="7" t="inlineStr">
+        <is>
+          <t>icap-2029</t>
+        </is>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>30th International Conference on Atomic Physics</t>
+        </is>
+      </c>
+      <c r="C132" s="7" t="inlineStr">
+        <is>
+          <t>ICAP 2029</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>quantum optics;nonlinear optics</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="H132" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="I132" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="J132" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="K132" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="L132" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="M132" s="7" t="inlineStr">
+        <is>
+          <t>https://www.icap29.com/</t>
+        </is>
+      </c>
+      <c r="N132" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O132" s="7" t="inlineStr">
+        <is>
+          <t>Atomic physics conference with quantum optics and light-matter interaction sessions</t>
+        </is>
+      </c>
+      <c r="P132" s="7" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="Q132" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="R132" s="7" t="inlineStr">
+        <is>
+          <t>new entry; year roll-over; triennial series, host not yet announced</t>
+        </is>
+      </c>
+      <c r="S132" s="7" t="inlineStr">
+        <is>
+          <t>https://www.icap29.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="7" t="inlineStr">
+        <is>
+          <t>iqt-nordics-2027</t>
+        </is>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>IQT Nordics 2027</t>
+        </is>
+      </c>
+      <c r="C133" s="7" t="inlineStr">
+        <is>
+          <t>IQT Nordics 2027</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>quantum communication;quantum computing hardware;integrated quantum photonics</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="H133" s="7" t="inlineStr">
+        <is>
+          <t>Copenhagen, Denmark</t>
+        </is>
+      </c>
+      <c r="I133" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="J133" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K133" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="L133" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="M133" s="7" t="inlineStr">
+        <is>
+          <t>https://iqtevent.com/nordics/</t>
+        </is>
+      </c>
+      <c r="N133" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O133" s="7" t="inlineStr">
+        <is>
+          <t>Nordic quantum industry conference with hardware and QKD sessions</t>
+        </is>
+      </c>
+      <c r="P133" s="7" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="Q133" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="R133" s="7" t="inlineStr">
+        <is>
+          <t>new entry; year roll-over; organizer confirmed Copenhagen return (rotation Copenhagen/Helsinki/Gothenburg/Oslo), exact dates TBA</t>
+        </is>
+      </c>
+      <c r="S133" s="7" t="inlineStr">
+        <is>
+          <t>https://iqtevent.com/nordics/; https://www.insidequantumtechnology.com/news-archive/announcing-the-return-of-iqt-nordics-in-copenhagen-2027/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="7" t="inlineStr">
+        <is>
+          <t>islc-2028</t>
+        </is>
+      </c>
+      <c r="B134" s="7" t="inlineStr">
+        <is>
+          <t>31st International Semiconductor Laser Conference</t>
+        </is>
+      </c>
+      <c r="C134" s="7" t="inlineStr">
+        <is>
+          <t>ISLC 2028</t>
+        </is>
+      </c>
+      <c r="D134" s="7" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
+        <is>
+          <t>single-photon sources;III-V on Si;photonic integrated circuits</t>
+        </is>
+      </c>
+      <c r="F134" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="H134" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="I134" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="J134" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="K134" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="L134" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="M134" s="7" t="inlineStr">
+        <is>
+          <t>https://ieeephotonics.org/conferences/</t>
+        </is>
+      </c>
+      <c r="N134" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="O134" s="7" t="inlineStr">
+        <is>
+          <t>III-V semiconductor laser conference — key for quantum light source development</t>
+        </is>
+      </c>
+      <c r="P134" s="7" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="Q134" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="R134" s="7" t="inlineStr">
+        <is>
+          <t>new entry; year roll-over; biennial series, host not yet announced</t>
+        </is>
+      </c>
+      <c r="S134" s="7" t="inlineStr">
+        <is>
+          <t>https://ieeephotonics.org/conferences/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>nrw-nano-2027</t>
+        </is>
+      </c>
+      <c r="B135" s="7" t="inlineStr">
+        <is>
+          <t>12th NRW Nano Conference</t>
+        </is>
+      </c>
+      <c r="C135" s="7" t="inlineStr">
+        <is>
+          <t>NRW Nano 2027</t>
+        </is>
+      </c>
+      <c r="D135" s="7" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
+        <is>
+          <t>nanophotonics;photonic integrated circuits</t>
+        </is>
+      </c>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="H135" s="7" t="inlineStr">
+        <is>
+          <t>North Rhine-Westphalia, Germany</t>
+        </is>
+      </c>
+      <c r="I135" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="J135" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="K135" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="L135" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="M135" s="7" t="inlineStr">
+        <is>
+          <t>https://www.nanoconference.de/</t>
+        </is>
+      </c>
+      <c r="N135" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O135" s="7" t="inlineStr">
+        <is>
+          <t>Regional NRW nanotechnology conference; local access</t>
+        </is>
+      </c>
+      <c r="P135" s="7" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="Q135" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="R135" s="7" t="inlineStr">
+        <is>
+          <t>renamed from 'nrw-nano-2026' placeholder; confirmed biennial series (11th ed. was Sep 30-Oct 1 2025, Dortmund), 2026 edition does not exist, next expected 2027 dates TBA</t>
+        </is>
+      </c>
+      <c r="S135" s="7" t="inlineStr">
+        <is>
+          <t>original list</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>oecc-2027</t>
+        </is>
+      </c>
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t>32nd OptoElectronics and Communications Conference</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>OECC 2027</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>photonic integrated circuits;silicon photonics;quantum communication</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="H136" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="I136" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="J136" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="K136" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="L136" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="M136" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="N136" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O136" s="7" t="inlineStr">
+        <is>
+          <t>Asia-Pacific optoelectronics and comms conference with PIC sessions</t>
+        </is>
+      </c>
+      <c r="P136" s="7" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="Q136" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="R136" s="7" t="inlineStr">
+        <is>
+          <t>new entry; year roll-over; annual, rotating Asia-Pacific host, 2027 not yet announced</t>
+        </is>
+      </c>
+      <c r="S136" s="7" t="inlineStr">
+        <is>
+          <t>original list</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="7" t="inlineStr">
+        <is>
+          <t>opic-2027</t>
+        </is>
+      </c>
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>OPIC 2027 — Optics &amp; Photonics International Congress</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t>OPIC 2027</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t>integrated quantum photonics;quantum optics;nanophotonics</t>
+        </is>
+      </c>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="H137" s="7" t="inlineStr">
+        <is>
+          <t>Yokohama, Japan (expected)</t>
+        </is>
+      </c>
+      <c r="I137" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="J137" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="K137" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="L137" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="M137" s="7" t="inlineStr">
+        <is>
+          <t>https://opicon.jp/</t>
+        </is>
+      </c>
+      <c r="N137" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O137" s="7" t="inlineStr">
+        <is>
+          <t>Japanese international photonics congress with quantum tracks</t>
+        </is>
+      </c>
+      <c r="P137" s="7" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="Q137" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="R137" s="7" t="inlineStr">
+        <is>
+          <t>new entry; annual series (every April, Pacifico Yokohama), 2027 dates not yet announced</t>
+        </is>
+      </c>
+      <c r="S137" s="7" t="inlineStr">
+        <is>
+          <t>https://opicon.jp/</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="7" t="inlineStr">
+        <is>
+          <t>optica-quantum-2028</t>
+        </is>
+      </c>
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t>Optica Quantum 2.0 Conference and Exhibition 2028</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
+          <t>Optica Quantum 2028</t>
+        </is>
+      </c>
+      <c r="D138" s="7" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t>integrated quantum photonics;quantum optics;single-photon sources;quantum communication;quantum computing hardware</t>
+        </is>
+      </c>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="G138" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="H138" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="I138" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="J138" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K138" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="L138" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="M138" s="7" t="inlineStr">
+        <is>
+          <t>https://www.optica.org/events/topical_meetings/quantum/</t>
+        </is>
+      </c>
+      <c r="N138" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="O138" s="7" t="inlineStr">
+        <is>
+          <t>Premier quantum photonics conference spanning PICs, detectors, QKD, and hardware</t>
+        </is>
+      </c>
+      <c r="P138" s="7" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="Q138" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="R138" s="7" t="inlineStr">
+        <is>
+          <t>new entry; year roll-over; biennial series, 2028 not yet announced</t>
+        </is>
+      </c>
+      <c r="S138" s="7" t="inlineStr">
+        <is>
+          <t>https://www.optica.org/events/topical_meetings/quantum/</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="7" t="inlineStr">
+        <is>
+          <t>owtnm-2027</t>
+        </is>
+      </c>
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t>OWTNM 2027 — Optical Wave &amp; Waveguide Theory and Modelling Workshop</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
+          <t>OWTNM 2027</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="inlineStr">
+        <is>
+          <t>Workshop</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>photonic integrated circuits;nanophotonics</t>
+        </is>
+      </c>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="H139" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="I139" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="J139" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K139" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="L139" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="M139" s="7" t="inlineStr">
+        <is>
+          <t>https://www.owtnm.eu/</t>
+        </is>
+      </c>
+      <c r="N139" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O139" s="7" t="inlineStr">
+        <is>
+          <t>Waveguide modelling workshop relevant to PIC simulation</t>
+        </is>
+      </c>
+      <c r="P139" s="7" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="Q139" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="R139" s="7" t="inlineStr">
+        <is>
+          <t>new entry; annual series since 1992, 2027 host not yet announced</t>
+        </is>
+      </c>
+      <c r="S139" s="7" t="inlineStr">
+        <is>
+          <t>https://www.owtnm.eu/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="7" t="inlineStr">
+        <is>
+          <t>photonics-north-2027</t>
+        </is>
+      </c>
+      <c r="B140" s="7" t="inlineStr">
+        <is>
+          <t>Photonics North 2027</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>PN 2027</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t>silicon photonics;integrated quantum photonics;quantum communication</t>
+        </is>
+      </c>
+      <c r="F140" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="H140" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="I140" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="J140" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="K140" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="L140" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="M140" s="7" t="inlineStr">
+        <is>
+          <t>https://photonicsnorth.com/en</t>
+        </is>
+      </c>
+      <c r="N140" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="O140" s="7" t="inlineStr">
+        <is>
+          <t>Canadian national photonics conference with PIC and quantum sessions</t>
+        </is>
+      </c>
+      <c r="P140" s="7" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="Q140" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="R140" s="7" t="inlineStr">
+        <is>
+          <t>new entry; year roll-over; cadence confirmed annual (2024 Vancouver, 2025 Ottawa, 2026 Québec City); 2027 not yet announced</t>
+        </is>
+      </c>
+      <c r="S140" s="7" t="inlineStr">
+        <is>
+          <t>https://photonicsnorth.com/en</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="inlineStr">
+        <is>
+          <t>quantum-korea-2027</t>
+        </is>
+      </c>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>Quantum Korea 2027</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr">
+        <is>
+          <t>Quantum Korea 2027</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="inlineStr">
+        <is>
+          <t>Conference</t>
+        </is>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>quantum computing hardware;quantum communication;integrated quantum photonics</t>
+        </is>
+      </c>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="H141" s="7" t="inlineStr">
+        <is>
+          <t>Seoul, South Korea (expected)</t>
+        </is>
+      </c>
+      <c r="I141" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="J141" s="7" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K141" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="L141" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="M141" s="7" t="inlineStr">
+        <is>
+          <t>https://quantum-korea.kr/en/main</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O141" s="7" t="inlineStr">
+        <is>
+          <t>Government-organised Korean quantum technology showcase</t>
+        </is>
+      </c>
+      <c r="P141" s="7" t="inlineStr">
+        <is>
+          <t>upcoming</t>
+        </is>
+      </c>
+      <c r="Q141" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-05</t>
+        </is>
+      </c>
+      <c r="R141" s="7" t="inlineStr">
+        <is>
+          <t>new entry; year roll-over; annual series since 2023, 2027 not yet announced</t>
+        </is>
+      </c>
+      <c r="S141" s="7" t="inlineStr">
+        <is>
+          <t>https://quantum-korea.kr/en/main</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="7" t="inlineStr">
+        <is>
           <t>spie-pfq-2027</t>
         </is>
       </c>
-      <c r="B130" s="7" t="inlineStr">
+      <c r="B142" s="7" t="inlineStr">
         <is>
           <t>SPIE Photonics for Quantum 2027</t>
         </is>
       </c>
-      <c r="C130" s="7" t="inlineStr">
+      <c r="C142" s="7" t="inlineStr">
         <is>
           <t>PfQ 2027</t>
         </is>
       </c>
-      <c r="D130" s="7" t="inlineStr">
+      <c r="D142" s="7" t="inlineStr">
         <is>
           <t>Conference</t>
         </is>
       </c>
-      <c r="E130" s="7" t="inlineStr">
+      <c r="E142" s="7" t="inlineStr">
         <is>
           <t>integrated quantum photonics;single-photon sources;quantum communication;quantum computing hardware</t>
         </is>
       </c>
-      <c r="F130" s="7" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="G130" s="7" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="H130" s="7" t="inlineStr">
+      <c r="F142" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="G142" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="H142" s="7" t="inlineStr">
         <is>
           <t>Waterloo, ON, Canada (expected)</t>
         </is>
       </c>
-      <c r="I130" s="7" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="J130" s="7" t="inlineStr">
+      <c r="I142" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="J142" s="7" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K130" s="7" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="L130" s="7" t="inlineStr">
-        <is>
-          <t>TBA</t>
-        </is>
-      </c>
-      <c r="M130" s="7" t="inlineStr">
+      <c r="K142" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="L142" s="7" t="inlineStr">
+        <is>
+          <t>TBA</t>
+        </is>
+      </c>
+      <c r="M142" s="7" t="inlineStr">
         <is>
           <t>https://spie.org/conferences-and-exhibitions/photonics-for-quantum</t>
         </is>
       </c>
-      <c r="N130" s="4" t="n">
+      <c r="N142" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="O130" s="7" t="inlineStr">
+      <c r="O142" s="7" t="inlineStr">
         <is>
           <t>Dedicated quantum photonics conference — bullseye for AG Schuck</t>
         </is>
       </c>
-      <c r="P130" s="7" t="inlineStr">
+      <c r="P142" s="7" t="inlineStr">
         <is>
           <t>upcoming</t>
         </is>
       </c>
-      <c r="Q130" s="7" t="inlineStr">
+      <c r="Q142" s="7" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="R130" s="7" t="inlineStr">
+      <c r="R142" s="7" t="inlineStr">
         <is>
           <t>new entry; year roll-over; annual series at Waterloo, 2027 dates not yet announced</t>
         </is>
       </c>
-      <c r="S130" s="7" t="inlineStr">
+      <c r="S142" s="7" t="inlineStr">
         <is>
           <t>https://spie.org/conferences-and-exhibitions/photonics-for-quantum</t>
         </is>
